--- a/harmonogram.xlsx
+++ b/harmonogram.xlsx
@@ -35,38 +35,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000FF11"/>
-        <bgColor rgb="0000FF11"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0000DBFF"/>
         <bgColor rgb="0000DBFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F88100"/>
-        <bgColor rgb="00F88100"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00004EFF"/>
         <bgColor rgb="00004EFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,8 +59,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F88100"/>
+        <bgColor rgb="00F88100"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00BA4EFF"/>
         <bgColor rgb="00BA4EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FF11"/>
+        <bgColor rgb="0000FF11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:CX10"/>
+  <dimension ref="A2:CX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="2" max="2"/>
@@ -604,8 +604,8 @@
       <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="n"/>
       <c r="N2" s="1" t="n"/>
-      <c r="O2" s="1" t="n"/>
-      <c r="P2" s="1" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
@@ -614,8 +614,8 @@
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="n"/>
-      <c r="Y2" s="2" t="n"/>
-      <c r="Z2" s="2" t="n"/>
+      <c r="Y2" s="3" t="n"/>
+      <c r="Z2" s="3" t="n"/>
       <c r="AA2" s="3" t="n"/>
       <c r="AB2" s="3" t="n"/>
       <c r="AC2" s="3" t="n"/>
@@ -624,8 +624,8 @@
       <c r="AF2" s="3" t="n"/>
       <c r="AG2" s="3" t="n"/>
       <c r="AH2" s="3" t="n"/>
-      <c r="AI2" s="3" t="n"/>
-      <c r="AJ2" s="3" t="n"/>
+      <c r="AI2" s="4" t="n"/>
+      <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n"/>
@@ -634,8 +634,8 @@
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
       <c r="AR2" s="4" t="n"/>
-      <c r="AS2" s="4" t="n"/>
-      <c r="AT2" s="4" t="n"/>
+      <c r="AS2" s="5" t="n"/>
+      <c r="AT2" s="5" t="n"/>
       <c r="AU2" s="5" t="n"/>
       <c r="AV2" s="5" t="n"/>
       <c r="AW2" s="5" t="n"/>
@@ -644,8 +644,8 @@
       <c r="AZ2" s="5" t="n"/>
       <c r="BA2" s="5" t="n"/>
       <c r="BB2" s="5" t="n"/>
-      <c r="BC2" s="5" t="n"/>
-      <c r="BD2" s="5" t="n"/>
+      <c r="BC2" s="6" t="n"/>
+      <c r="BD2" s="6" t="n"/>
       <c r="BE2" s="6" t="n"/>
       <c r="BF2" s="6" t="n"/>
       <c r="BG2" s="6" t="n"/>
@@ -654,8 +654,8 @@
       <c r="BJ2" s="6" t="n"/>
       <c r="BK2" s="6" t="n"/>
       <c r="BL2" s="6" t="n"/>
-      <c r="BM2" s="6" t="n"/>
-      <c r="BN2" s="6" t="n"/>
+      <c r="BM2" s="7" t="n"/>
+      <c r="BN2" s="7" t="n"/>
       <c r="BO2" s="7" t="n"/>
       <c r="BP2" s="7" t="n"/>
       <c r="BQ2" s="7" t="n"/>
@@ -664,8 +664,8 @@
       <c r="BT2" s="7" t="n"/>
       <c r="BU2" s="7" t="n"/>
       <c r="BV2" s="7" t="n"/>
-      <c r="BW2" s="7" t="n"/>
-      <c r="BX2" s="7" t="n"/>
+      <c r="BW2" s="8" t="n"/>
+      <c r="BX2" s="8" t="n"/>
       <c r="BY2" s="8" t="n"/>
       <c r="BZ2" s="8" t="n"/>
       <c r="CA2" s="8" t="n"/>
@@ -674,8 +674,8 @@
       <c r="CD2" s="8" t="n"/>
       <c r="CE2" s="8" t="n"/>
       <c r="CF2" s="8" t="n"/>
-      <c r="CG2" s="8" t="n"/>
-      <c r="CH2" s="8" t="n"/>
+      <c r="CG2" s="9" t="n"/>
+      <c r="CH2" s="9" t="n"/>
       <c r="CI2" s="9" t="n"/>
       <c r="CJ2" s="9" t="n"/>
       <c r="CK2" s="9" t="n"/>
@@ -698,106 +698,106 @@
           <t>Maszyna 2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="6" t="n"/>
-      <c r="M3" s="6" t="n"/>
-      <c r="N3" s="6" t="n"/>
-      <c r="O3" s="6" t="n"/>
-      <c r="P3" s="7" t="n"/>
-      <c r="Q3" s="7" t="n"/>
-      <c r="R3" s="7" t="n"/>
-      <c r="S3" s="7" t="n"/>
-      <c r="T3" s="7" t="n"/>
-      <c r="U3" s="7" t="n"/>
-      <c r="V3" s="7" t="n"/>
-      <c r="W3" s="7" t="n"/>
-      <c r="X3" s="7" t="n"/>
-      <c r="Y3" s="7" t="n"/>
-      <c r="Z3" s="8" t="n"/>
-      <c r="AA3" s="8" t="n"/>
-      <c r="AB3" s="8" t="n"/>
-      <c r="AC3" s="8" t="n"/>
-      <c r="AD3" s="8" t="n"/>
-      <c r="AE3" s="8" t="n"/>
-      <c r="AF3" s="8" t="n"/>
-      <c r="AG3" s="8" t="n"/>
-      <c r="AH3" s="8" t="n"/>
-      <c r="AI3" s="8" t="n"/>
-      <c r="AJ3" s="9" t="n"/>
-      <c r="AK3" s="9" t="n"/>
-      <c r="AL3" s="9" t="n"/>
-      <c r="AM3" s="9" t="n"/>
-      <c r="AN3" s="9" t="n"/>
-      <c r="AO3" s="9" t="n"/>
-      <c r="AP3" s="9" t="n"/>
-      <c r="AQ3" s="9" t="n"/>
-      <c r="AR3" s="9" t="n"/>
-      <c r="AS3" s="9" t="n"/>
-      <c r="AT3" s="1" t="n"/>
-      <c r="AU3" s="1" t="n"/>
-      <c r="AV3" s="1" t="n"/>
-      <c r="AW3" s="1" t="n"/>
-      <c r="AX3" s="1" t="n"/>
-      <c r="AY3" s="1" t="n"/>
-      <c r="AZ3" s="1" t="n"/>
-      <c r="BA3" s="1" t="n"/>
-      <c r="BB3" s="1" t="n"/>
-      <c r="BC3" s="1" t="n"/>
-      <c r="BD3" s="2" t="n"/>
-      <c r="BE3" s="2" t="n"/>
-      <c r="BF3" s="2" t="n"/>
-      <c r="BG3" s="2" t="n"/>
-      <c r="BH3" s="2" t="n"/>
-      <c r="BI3" s="2" t="n"/>
-      <c r="BJ3" s="2" t="n"/>
-      <c r="BK3" s="2" t="n"/>
-      <c r="BL3" s="2" t="n"/>
-      <c r="BM3" s="2" t="n"/>
-      <c r="BN3" s="3" t="n"/>
-      <c r="BO3" s="3" t="n"/>
-      <c r="BP3" s="3" t="n"/>
-      <c r="BQ3" s="3" t="n"/>
-      <c r="BR3" s="3" t="n"/>
-      <c r="BS3" s="3" t="n"/>
-      <c r="BT3" s="3" t="n"/>
-      <c r="BU3" s="3" t="n"/>
-      <c r="BV3" s="3" t="n"/>
-      <c r="BW3" s="3" t="n"/>
-      <c r="BX3" s="4" t="n"/>
-      <c r="BY3" s="4" t="n"/>
-      <c r="BZ3" s="4" t="n"/>
-      <c r="CA3" s="4" t="n"/>
-      <c r="CB3" s="4" t="n"/>
-      <c r="CC3" s="4" t="n"/>
-      <c r="CD3" s="4" t="n"/>
-      <c r="CE3" s="4" t="n"/>
-      <c r="CF3" s="4" t="n"/>
-      <c r="CG3" s="4" t="n"/>
-      <c r="CH3" s="5" t="n"/>
-      <c r="CI3" s="5" t="n"/>
-      <c r="CJ3" s="5" t="n"/>
-      <c r="CK3" s="5" t="n"/>
-      <c r="CL3" s="5" t="n"/>
-      <c r="CM3" s="5" t="n"/>
-      <c r="CN3" s="5" t="n"/>
-      <c r="CO3" s="5" t="n"/>
-      <c r="CP3" s="5" t="n"/>
-      <c r="CQ3" s="5" t="n"/>
-      <c r="CR3" s="5" t="n"/>
-      <c r="CS3" s="5" t="n"/>
-      <c r="CT3" s="5" t="n"/>
-      <c r="CU3" s="5" t="n"/>
-      <c r="CV3" s="5" t="n"/>
-      <c r="CW3" s="5" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="4" t="n"/>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" s="5" t="n"/>
+      <c r="T3" s="5" t="n"/>
+      <c r="U3" s="5" t="n"/>
+      <c r="V3" s="5" t="n"/>
+      <c r="W3" s="5" t="n"/>
+      <c r="X3" s="5" t="n"/>
+      <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="5" t="n"/>
+      <c r="AA3" s="5" t="n"/>
+      <c r="AB3" s="6" t="n"/>
+      <c r="AC3" s="6" t="n"/>
+      <c r="AD3" s="6" t="n"/>
+      <c r="AE3" s="6" t="n"/>
+      <c r="AF3" s="6" t="n"/>
+      <c r="AG3" s="6" t="n"/>
+      <c r="AH3" s="6" t="n"/>
+      <c r="AI3" s="6" t="n"/>
+      <c r="AJ3" s="6" t="n"/>
+      <c r="AK3" s="6" t="n"/>
+      <c r="AL3" s="7" t="n"/>
+      <c r="AM3" s="7" t="n"/>
+      <c r="AN3" s="7" t="n"/>
+      <c r="AO3" s="7" t="n"/>
+      <c r="AP3" s="7" t="n"/>
+      <c r="AQ3" s="7" t="n"/>
+      <c r="AR3" s="7" t="n"/>
+      <c r="AS3" s="7" t="n"/>
+      <c r="AT3" s="7" t="n"/>
+      <c r="AU3" s="7" t="n"/>
+      <c r="AV3" s="8" t="n"/>
+      <c r="AW3" s="8" t="n"/>
+      <c r="AX3" s="8" t="n"/>
+      <c r="AY3" s="8" t="n"/>
+      <c r="AZ3" s="8" t="n"/>
+      <c r="BA3" s="8" t="n"/>
+      <c r="BB3" s="8" t="n"/>
+      <c r="BC3" s="8" t="n"/>
+      <c r="BD3" s="8" t="n"/>
+      <c r="BE3" s="8" t="n"/>
+      <c r="BF3" s="9" t="n"/>
+      <c r="BG3" s="9" t="n"/>
+      <c r="BH3" s="9" t="n"/>
+      <c r="BI3" s="9" t="n"/>
+      <c r="BJ3" s="9" t="n"/>
+      <c r="BK3" s="9" t="n"/>
+      <c r="BL3" s="9" t="n"/>
+      <c r="BM3" s="9" t="n"/>
+      <c r="BN3" s="9" t="n"/>
+      <c r="BO3" s="9" t="n"/>
+      <c r="BP3" s="1" t="n"/>
+      <c r="BQ3" s="1" t="n"/>
+      <c r="BR3" s="1" t="n"/>
+      <c r="BS3" s="1" t="n"/>
+      <c r="BT3" s="1" t="n"/>
+      <c r="BU3" s="1" t="n"/>
+      <c r="BV3" s="1" t="n"/>
+      <c r="BW3" s="1" t="n"/>
+      <c r="BX3" s="1" t="n"/>
+      <c r="BY3" s="1" t="n"/>
+      <c r="BZ3" s="2" t="n"/>
+      <c r="CA3" s="2" t="n"/>
+      <c r="CB3" s="2" t="n"/>
+      <c r="CC3" s="2" t="n"/>
+      <c r="CD3" s="2" t="n"/>
+      <c r="CE3" s="2" t="n"/>
+      <c r="CF3" s="2" t="n"/>
+      <c r="CG3" s="2" t="n"/>
+      <c r="CH3" s="2" t="n"/>
+      <c r="CI3" s="2" t="n"/>
+      <c r="CJ3" s="3" t="n"/>
+      <c r="CK3" s="3" t="n"/>
+      <c r="CL3" s="3" t="n"/>
+      <c r="CM3" s="3" t="n"/>
+      <c r="CN3" s="3" t="n"/>
+      <c r="CO3" s="3" t="n"/>
+      <c r="CP3" s="3" t="n"/>
+      <c r="CQ3" s="3" t="n"/>
+      <c r="CR3" s="3" t="n"/>
+      <c r="CS3" s="3" t="n"/>
+      <c r="CT3" s="3" t="n"/>
+      <c r="CU3" s="3" t="n"/>
+      <c r="CV3" s="3" t="n"/>
+      <c r="CW3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -817,80 +817,80 @@
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
       <c r="R4" s="5" t="n"/>
       <c r="S4" s="5" t="n"/>
       <c r="T4" s="5" t="n"/>
       <c r="U4" s="5" t="n"/>
       <c r="V4" s="5" t="n"/>
       <c r="W4" s="5" t="n"/>
-      <c r="X4" s="5" t="n"/>
-      <c r="Y4" s="5" t="n"/>
-      <c r="Z4" s="5" t="n"/>
-      <c r="AA4" s="5" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="6" t="n"/>
+      <c r="Z4" s="6" t="n"/>
+      <c r="AA4" s="6" t="n"/>
       <c r="AB4" s="6" t="n"/>
       <c r="AC4" s="6" t="n"/>
       <c r="AD4" s="6" t="n"/>
       <c r="AE4" s="6" t="n"/>
       <c r="AF4" s="6" t="n"/>
       <c r="AG4" s="6" t="n"/>
-      <c r="AH4" s="6" t="n"/>
-      <c r="AI4" s="6" t="n"/>
-      <c r="AJ4" s="6" t="n"/>
-      <c r="AK4" s="6" t="n"/>
+      <c r="AH4" s="7" t="n"/>
+      <c r="AI4" s="7" t="n"/>
+      <c r="AJ4" s="7" t="n"/>
+      <c r="AK4" s="7" t="n"/>
       <c r="AL4" s="7" t="n"/>
       <c r="AM4" s="7" t="n"/>
       <c r="AN4" s="7" t="n"/>
       <c r="AO4" s="7" t="n"/>
       <c r="AP4" s="7" t="n"/>
       <c r="AQ4" s="7" t="n"/>
-      <c r="AR4" s="7" t="n"/>
-      <c r="AS4" s="7" t="n"/>
-      <c r="AT4" s="7" t="n"/>
-      <c r="AU4" s="7" t="n"/>
+      <c r="AR4" s="8" t="n"/>
+      <c r="AS4" s="8" t="n"/>
+      <c r="AT4" s="8" t="n"/>
+      <c r="AU4" s="8" t="n"/>
       <c r="AV4" s="8" t="n"/>
       <c r="AW4" s="8" t="n"/>
       <c r="AX4" s="8" t="n"/>
       <c r="AY4" s="8" t="n"/>
       <c r="AZ4" s="8" t="n"/>
       <c r="BA4" s="8" t="n"/>
-      <c r="BB4" s="8" t="n"/>
-      <c r="BC4" s="8" t="n"/>
-      <c r="BD4" s="8" t="n"/>
-      <c r="BE4" s="8" t="n"/>
+      <c r="BB4" s="9" t="n"/>
+      <c r="BC4" s="9" t="n"/>
+      <c r="BD4" s="9" t="n"/>
+      <c r="BE4" s="9" t="n"/>
       <c r="BF4" s="9" t="n"/>
       <c r="BG4" s="9" t="n"/>
       <c r="BH4" s="9" t="n"/>
       <c r="BI4" s="9" t="n"/>
       <c r="BJ4" s="9" t="n"/>
       <c r="BK4" s="9" t="n"/>
-      <c r="BL4" s="9" t="n"/>
-      <c r="BM4" s="9" t="n"/>
-      <c r="BN4" s="9" t="n"/>
-      <c r="BO4" s="9" t="n"/>
+      <c r="BL4" s="1" t="n"/>
+      <c r="BM4" s="1" t="n"/>
+      <c r="BN4" s="1" t="n"/>
+      <c r="BO4" s="1" t="n"/>
       <c r="BP4" s="1" t="n"/>
       <c r="BQ4" s="1" t="n"/>
       <c r="BR4" s="1" t="n"/>
       <c r="BS4" s="1" t="n"/>
       <c r="BT4" s="1" t="n"/>
       <c r="BU4" s="1" t="n"/>
-      <c r="BV4" s="1" t="n"/>
-      <c r="BW4" s="1" t="n"/>
-      <c r="BX4" s="1" t="n"/>
-      <c r="BY4" s="1" t="n"/>
+      <c r="BV4" s="2" t="n"/>
+      <c r="BW4" s="2" t="n"/>
+      <c r="BX4" s="2" t="n"/>
+      <c r="BY4" s="2" t="n"/>
       <c r="BZ4" s="2" t="n"/>
       <c r="CA4" s="2" t="n"/>
       <c r="CB4" s="2" t="n"/>
       <c r="CC4" s="2" t="n"/>
       <c r="CD4" s="2" t="n"/>
       <c r="CE4" s="2" t="n"/>
-      <c r="CF4" s="2" t="n"/>
-      <c r="CG4" s="2" t="n"/>
-      <c r="CH4" s="2" t="n"/>
-      <c r="CI4" s="2" t="n"/>
+      <c r="CF4" s="3" t="n"/>
+      <c r="CG4" s="3" t="n"/>
+      <c r="CH4" s="3" t="n"/>
+      <c r="CI4" s="3" t="n"/>
       <c r="CJ4" s="3" t="n"/>
       <c r="CK4" s="3" t="n"/>
       <c r="CL4" s="3" t="n"/>
@@ -925,8 +925,8 @@
       <c r="L5" s="1" t="n"/>
       <c r="M5" s="1" t="n"/>
       <c r="N5" s="1" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
+      <c r="O5" s="1" t="n"/>
+      <c r="P5" s="1" t="n"/>
       <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
@@ -935,8 +935,8 @@
       <c r="V5" s="2" t="n"/>
       <c r="W5" s="2" t="n"/>
       <c r="X5" s="2" t="n"/>
-      <c r="Y5" s="3" t="n"/>
-      <c r="Z5" s="3" t="n"/>
+      <c r="Y5" s="2" t="n"/>
+      <c r="Z5" s="2" t="n"/>
       <c r="AA5" s="3" t="n"/>
       <c r="AB5" s="3" t="n"/>
       <c r="AC5" s="3" t="n"/>
@@ -945,8 +945,8 @@
       <c r="AF5" s="3" t="n"/>
       <c r="AG5" s="3" t="n"/>
       <c r="AH5" s="3" t="n"/>
-      <c r="AI5" s="4" t="n"/>
-      <c r="AJ5" s="4" t="n"/>
+      <c r="AI5" s="3" t="n"/>
+      <c r="AJ5" s="3" t="n"/>
       <c r="AK5" s="4" t="n"/>
       <c r="AL5" s="4" t="n"/>
       <c r="AM5" s="4" t="n"/>
@@ -955,8 +955,8 @@
       <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
       <c r="AR5" s="4" t="n"/>
-      <c r="AS5" s="5" t="n"/>
-      <c r="AT5" s="5" t="n"/>
+      <c r="AS5" s="4" t="n"/>
+      <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="5" t="n"/>
       <c r="AV5" s="5" t="n"/>
       <c r="AW5" s="5" t="n"/>
@@ -965,8 +965,8 @@
       <c r="AZ5" s="5" t="n"/>
       <c r="BA5" s="5" t="n"/>
       <c r="BB5" s="5" t="n"/>
-      <c r="BC5" s="6" t="n"/>
-      <c r="BD5" s="6" t="n"/>
+      <c r="BC5" s="5" t="n"/>
+      <c r="BD5" s="5" t="n"/>
       <c r="BE5" s="6" t="n"/>
       <c r="BF5" s="6" t="n"/>
       <c r="BG5" s="6" t="n"/>
@@ -975,8 +975,8 @@
       <c r="BJ5" s="6" t="n"/>
       <c r="BK5" s="6" t="n"/>
       <c r="BL5" s="6" t="n"/>
-      <c r="BM5" s="7" t="n"/>
-      <c r="BN5" s="7" t="n"/>
+      <c r="BM5" s="6" t="n"/>
+      <c r="BN5" s="6" t="n"/>
       <c r="BO5" s="7" t="n"/>
       <c r="BP5" s="7" t="n"/>
       <c r="BQ5" s="7" t="n"/>
@@ -985,8 +985,8 @@
       <c r="BT5" s="7" t="n"/>
       <c r="BU5" s="7" t="n"/>
       <c r="BV5" s="7" t="n"/>
-      <c r="BW5" s="8" t="n"/>
-      <c r="BX5" s="8" t="n"/>
+      <c r="BW5" s="7" t="n"/>
+      <c r="BX5" s="7" t="n"/>
       <c r="BY5" s="8" t="n"/>
       <c r="BZ5" s="8" t="n"/>
       <c r="CA5" s="8" t="n"/>
@@ -995,8 +995,8 @@
       <c r="CD5" s="8" t="n"/>
       <c r="CE5" s="8" t="n"/>
       <c r="CF5" s="8" t="n"/>
-      <c r="CG5" s="9" t="n"/>
-      <c r="CH5" s="9" t="n"/>
+      <c r="CG5" s="8" t="n"/>
+      <c r="CH5" s="8" t="n"/>
       <c r="CI5" s="9" t="n"/>
       <c r="CJ5" s="9" t="n"/>
       <c r="CK5" s="9" t="n"/>
@@ -1019,106 +1019,106 @@
           <t>Maszyna 5</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n"/>
-      <c r="O6" s="8" t="n"/>
-      <c r="P6" s="8" t="n"/>
-      <c r="Q6" s="8" t="n"/>
-      <c r="R6" s="8" t="n"/>
-      <c r="S6" s="8" t="n"/>
-      <c r="T6" s="8" t="n"/>
-      <c r="U6" s="8" t="n"/>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="9" t="n"/>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="9" t="n"/>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="9" t="n"/>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="1" t="n"/>
-      <c r="AG6" s="1" t="n"/>
-      <c r="AH6" s="1" t="n"/>
-      <c r="AI6" s="1" t="n"/>
-      <c r="AJ6" s="1" t="n"/>
-      <c r="AK6" s="1" t="n"/>
-      <c r="AL6" s="1" t="n"/>
-      <c r="AM6" s="1" t="n"/>
-      <c r="AN6" s="1" t="n"/>
-      <c r="AO6" s="1" t="n"/>
-      <c r="AP6" s="2" t="n"/>
-      <c r="AQ6" s="2" t="n"/>
-      <c r="AR6" s="2" t="n"/>
-      <c r="AS6" s="2" t="n"/>
-      <c r="AT6" s="2" t="n"/>
-      <c r="AU6" s="2" t="n"/>
-      <c r="AV6" s="2" t="n"/>
-      <c r="AW6" s="2" t="n"/>
-      <c r="AX6" s="2" t="n"/>
-      <c r="AY6" s="2" t="n"/>
-      <c r="AZ6" s="3" t="n"/>
-      <c r="BA6" s="3" t="n"/>
-      <c r="BB6" s="3" t="n"/>
-      <c r="BC6" s="3" t="n"/>
-      <c r="BD6" s="3" t="n"/>
-      <c r="BE6" s="3" t="n"/>
-      <c r="BF6" s="3" t="n"/>
-      <c r="BG6" s="3" t="n"/>
-      <c r="BH6" s="3" t="n"/>
-      <c r="BI6" s="3" t="n"/>
-      <c r="BJ6" s="4" t="n"/>
-      <c r="BK6" s="4" t="n"/>
-      <c r="BL6" s="4" t="n"/>
-      <c r="BM6" s="4" t="n"/>
-      <c r="BN6" s="4" t="n"/>
-      <c r="BO6" s="4" t="n"/>
-      <c r="BP6" s="4" t="n"/>
-      <c r="BQ6" s="4" t="n"/>
-      <c r="BR6" s="4" t="n"/>
-      <c r="BS6" s="4" t="n"/>
-      <c r="BT6" s="5" t="n"/>
-      <c r="BU6" s="5" t="n"/>
-      <c r="BV6" s="5" t="n"/>
-      <c r="BW6" s="5" t="n"/>
-      <c r="BX6" s="5" t="n"/>
-      <c r="BY6" s="5" t="n"/>
-      <c r="BZ6" s="5" t="n"/>
-      <c r="CA6" s="5" t="n"/>
-      <c r="CB6" s="5" t="n"/>
-      <c r="CC6" s="5" t="n"/>
-      <c r="CD6" s="6" t="n"/>
-      <c r="CE6" s="6" t="n"/>
-      <c r="CF6" s="6" t="n"/>
-      <c r="CG6" s="6" t="n"/>
-      <c r="CH6" s="6" t="n"/>
-      <c r="CI6" s="6" t="n"/>
-      <c r="CJ6" s="6" t="n"/>
-      <c r="CK6" s="6" t="n"/>
-      <c r="CL6" s="6" t="n"/>
-      <c r="CM6" s="6" t="n"/>
-      <c r="CN6" s="6" t="n"/>
-      <c r="CO6" s="6" t="n"/>
-      <c r="CP6" s="6" t="n"/>
-      <c r="CQ6" s="6" t="n"/>
-      <c r="CR6" s="6" t="n"/>
-      <c r="CS6" s="6" t="n"/>
-      <c r="CT6" s="6" t="n"/>
-      <c r="CU6" s="6" t="n"/>
-      <c r="CV6" s="6" t="n"/>
-      <c r="CW6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="7" t="n"/>
+      <c r="Q6" s="7" t="n"/>
+      <c r="R6" s="7" t="n"/>
+      <c r="S6" s="7" t="n"/>
+      <c r="T6" s="7" t="n"/>
+      <c r="U6" s="7" t="n"/>
+      <c r="V6" s="7" t="n"/>
+      <c r="W6" s="7" t="n"/>
+      <c r="X6" s="7" t="n"/>
+      <c r="Y6" s="7" t="n"/>
+      <c r="Z6" s="8" t="n"/>
+      <c r="AA6" s="8" t="n"/>
+      <c r="AB6" s="8" t="n"/>
+      <c r="AC6" s="8" t="n"/>
+      <c r="AD6" s="8" t="n"/>
+      <c r="AE6" s="8" t="n"/>
+      <c r="AF6" s="8" t="n"/>
+      <c r="AG6" s="8" t="n"/>
+      <c r="AH6" s="8" t="n"/>
+      <c r="AI6" s="8" t="n"/>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="9" t="n"/>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="9" t="n"/>
+      <c r="AP6" s="9" t="n"/>
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="9" t="n"/>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="1" t="n"/>
+      <c r="AU6" s="1" t="n"/>
+      <c r="AV6" s="1" t="n"/>
+      <c r="AW6" s="1" t="n"/>
+      <c r="AX6" s="1" t="n"/>
+      <c r="AY6" s="1" t="n"/>
+      <c r="AZ6" s="1" t="n"/>
+      <c r="BA6" s="1" t="n"/>
+      <c r="BB6" s="1" t="n"/>
+      <c r="BC6" s="1" t="n"/>
+      <c r="BD6" s="2" t="n"/>
+      <c r="BE6" s="2" t="n"/>
+      <c r="BF6" s="2" t="n"/>
+      <c r="BG6" s="2" t="n"/>
+      <c r="BH6" s="2" t="n"/>
+      <c r="BI6" s="2" t="n"/>
+      <c r="BJ6" s="2" t="n"/>
+      <c r="BK6" s="2" t="n"/>
+      <c r="BL6" s="2" t="n"/>
+      <c r="BM6" s="2" t="n"/>
+      <c r="BN6" s="3" t="n"/>
+      <c r="BO6" s="3" t="n"/>
+      <c r="BP6" s="3" t="n"/>
+      <c r="BQ6" s="3" t="n"/>
+      <c r="BR6" s="3" t="n"/>
+      <c r="BS6" s="3" t="n"/>
+      <c r="BT6" s="3" t="n"/>
+      <c r="BU6" s="3" t="n"/>
+      <c r="BV6" s="3" t="n"/>
+      <c r="BW6" s="3" t="n"/>
+      <c r="BX6" s="4" t="n"/>
+      <c r="BY6" s="4" t="n"/>
+      <c r="BZ6" s="4" t="n"/>
+      <c r="CA6" s="4" t="n"/>
+      <c r="CB6" s="4" t="n"/>
+      <c r="CC6" s="4" t="n"/>
+      <c r="CD6" s="4" t="n"/>
+      <c r="CE6" s="4" t="n"/>
+      <c r="CF6" s="4" t="n"/>
+      <c r="CG6" s="4" t="n"/>
+      <c r="CH6" s="5" t="n"/>
+      <c r="CI6" s="5" t="n"/>
+      <c r="CJ6" s="5" t="n"/>
+      <c r="CK6" s="5" t="n"/>
+      <c r="CL6" s="5" t="n"/>
+      <c r="CM6" s="5" t="n"/>
+      <c r="CN6" s="5" t="n"/>
+      <c r="CO6" s="5" t="n"/>
+      <c r="CP6" s="5" t="n"/>
+      <c r="CQ6" s="5" t="n"/>
+      <c r="CR6" s="5" t="n"/>
+      <c r="CS6" s="5" t="n"/>
+      <c r="CT6" s="5" t="n"/>
+      <c r="CU6" s="5" t="n"/>
+      <c r="CV6" s="5" t="n"/>
+      <c r="CW6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1126,106 +1126,106 @@
           <t>Maszyna 6</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="7" t="n"/>
-      <c r="P7" s="7" t="n"/>
-      <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="7" t="n"/>
-      <c r="S7" s="7" t="n"/>
-      <c r="T7" s="7" t="n"/>
-      <c r="U7" s="7" t="n"/>
-      <c r="V7" s="7" t="n"/>
-      <c r="W7" s="8" t="n"/>
-      <c r="X7" s="8" t="n"/>
-      <c r="Y7" s="8" t="n"/>
-      <c r="Z7" s="8" t="n"/>
-      <c r="AA7" s="8" t="n"/>
-      <c r="AB7" s="8" t="n"/>
-      <c r="AC7" s="8" t="n"/>
-      <c r="AD7" s="8" t="n"/>
-      <c r="AE7" s="8" t="n"/>
-      <c r="AF7" s="8" t="n"/>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="9" t="n"/>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="9" t="n"/>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="9" t="n"/>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="1" t="n"/>
-      <c r="AR7" s="1" t="n"/>
-      <c r="AS7" s="1" t="n"/>
-      <c r="AT7" s="1" t="n"/>
-      <c r="AU7" s="1" t="n"/>
-      <c r="AV7" s="1" t="n"/>
-      <c r="AW7" s="1" t="n"/>
-      <c r="AX7" s="1" t="n"/>
-      <c r="AY7" s="1" t="n"/>
-      <c r="AZ7" s="1" t="n"/>
-      <c r="BA7" s="2" t="n"/>
-      <c r="BB7" s="2" t="n"/>
-      <c r="BC7" s="2" t="n"/>
-      <c r="BD7" s="2" t="n"/>
-      <c r="BE7" s="2" t="n"/>
-      <c r="BF7" s="2" t="n"/>
-      <c r="BG7" s="2" t="n"/>
-      <c r="BH7" s="2" t="n"/>
-      <c r="BI7" s="2" t="n"/>
-      <c r="BJ7" s="2" t="n"/>
-      <c r="BK7" s="3" t="n"/>
-      <c r="BL7" s="3" t="n"/>
-      <c r="BM7" s="3" t="n"/>
-      <c r="BN7" s="3" t="n"/>
-      <c r="BO7" s="3" t="n"/>
-      <c r="BP7" s="3" t="n"/>
-      <c r="BQ7" s="3" t="n"/>
-      <c r="BR7" s="3" t="n"/>
-      <c r="BS7" s="3" t="n"/>
-      <c r="BT7" s="3" t="n"/>
-      <c r="BU7" s="4" t="n"/>
-      <c r="BV7" s="4" t="n"/>
-      <c r="BW7" s="4" t="n"/>
-      <c r="BX7" s="4" t="n"/>
-      <c r="BY7" s="4" t="n"/>
-      <c r="BZ7" s="4" t="n"/>
-      <c r="CA7" s="4" t="n"/>
-      <c r="CB7" s="4" t="n"/>
-      <c r="CC7" s="4" t="n"/>
-      <c r="CD7" s="4" t="n"/>
-      <c r="CE7" s="5" t="n"/>
-      <c r="CF7" s="5" t="n"/>
-      <c r="CG7" s="5" t="n"/>
-      <c r="CH7" s="5" t="n"/>
-      <c r="CI7" s="5" t="n"/>
-      <c r="CJ7" s="5" t="n"/>
-      <c r="CK7" s="5" t="n"/>
-      <c r="CL7" s="5" t="n"/>
-      <c r="CM7" s="5" t="n"/>
-      <c r="CN7" s="5" t="n"/>
-      <c r="CO7" s="5" t="n"/>
-      <c r="CP7" s="5" t="n"/>
-      <c r="CQ7" s="5" t="n"/>
-      <c r="CR7" s="5" t="n"/>
-      <c r="CS7" s="5" t="n"/>
-      <c r="CT7" s="5" t="n"/>
-      <c r="CU7" s="5" t="n"/>
-      <c r="CV7" s="5" t="n"/>
-      <c r="CW7" s="5" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="9" t="n"/>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="9" t="n"/>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="9" t="n"/>
+      <c r="AD7" s="9" t="n"/>
+      <c r="AE7" s="9" t="n"/>
+      <c r="AF7" s="1" t="n"/>
+      <c r="AG7" s="1" t="n"/>
+      <c r="AH7" s="1" t="n"/>
+      <c r="AI7" s="1" t="n"/>
+      <c r="AJ7" s="1" t="n"/>
+      <c r="AK7" s="1" t="n"/>
+      <c r="AL7" s="1" t="n"/>
+      <c r="AM7" s="1" t="n"/>
+      <c r="AN7" s="1" t="n"/>
+      <c r="AO7" s="1" t="n"/>
+      <c r="AP7" s="2" t="n"/>
+      <c r="AQ7" s="2" t="n"/>
+      <c r="AR7" s="2" t="n"/>
+      <c r="AS7" s="2" t="n"/>
+      <c r="AT7" s="2" t="n"/>
+      <c r="AU7" s="2" t="n"/>
+      <c r="AV7" s="2" t="n"/>
+      <c r="AW7" s="2" t="n"/>
+      <c r="AX7" s="2" t="n"/>
+      <c r="AY7" s="2" t="n"/>
+      <c r="AZ7" s="3" t="n"/>
+      <c r="BA7" s="3" t="n"/>
+      <c r="BB7" s="3" t="n"/>
+      <c r="BC7" s="3" t="n"/>
+      <c r="BD7" s="3" t="n"/>
+      <c r="BE7" s="3" t="n"/>
+      <c r="BF7" s="3" t="n"/>
+      <c r="BG7" s="3" t="n"/>
+      <c r="BH7" s="3" t="n"/>
+      <c r="BI7" s="3" t="n"/>
+      <c r="BJ7" s="4" t="n"/>
+      <c r="BK7" s="4" t="n"/>
+      <c r="BL7" s="4" t="n"/>
+      <c r="BM7" s="4" t="n"/>
+      <c r="BN7" s="4" t="n"/>
+      <c r="BO7" s="4" t="n"/>
+      <c r="BP7" s="4" t="n"/>
+      <c r="BQ7" s="4" t="n"/>
+      <c r="BR7" s="4" t="n"/>
+      <c r="BS7" s="4" t="n"/>
+      <c r="BT7" s="5" t="n"/>
+      <c r="BU7" s="5" t="n"/>
+      <c r="BV7" s="5" t="n"/>
+      <c r="BW7" s="5" t="n"/>
+      <c r="BX7" s="5" t="n"/>
+      <c r="BY7" s="5" t="n"/>
+      <c r="BZ7" s="5" t="n"/>
+      <c r="CA7" s="5" t="n"/>
+      <c r="CB7" s="5" t="n"/>
+      <c r="CC7" s="5" t="n"/>
+      <c r="CD7" s="6" t="n"/>
+      <c r="CE7" s="6" t="n"/>
+      <c r="CF7" s="6" t="n"/>
+      <c r="CG7" s="6" t="n"/>
+      <c r="CH7" s="6" t="n"/>
+      <c r="CI7" s="6" t="n"/>
+      <c r="CJ7" s="6" t="n"/>
+      <c r="CK7" s="6" t="n"/>
+      <c r="CL7" s="6" t="n"/>
+      <c r="CM7" s="6" t="n"/>
+      <c r="CN7" s="6" t="n"/>
+      <c r="CO7" s="6" t="n"/>
+      <c r="CP7" s="6" t="n"/>
+      <c r="CQ7" s="6" t="n"/>
+      <c r="CR7" s="6" t="n"/>
+      <c r="CS7" s="6" t="n"/>
+      <c r="CT7" s="6" t="n"/>
+      <c r="CU7" s="6" t="n"/>
+      <c r="CV7" s="6" t="n"/>
+      <c r="CW7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1244,82 +1244,82 @@
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
+      <c r="M8" s="7" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="7" t="n"/>
       <c r="S8" s="7" t="n"/>
       <c r="T8" s="7" t="n"/>
       <c r="U8" s="7" t="n"/>
       <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
-      <c r="AA8" s="7" t="n"/>
-      <c r="AB8" s="7" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
       <c r="AC8" s="8" t="n"/>
       <c r="AD8" s="8" t="n"/>
       <c r="AE8" s="8" t="n"/>
       <c r="AF8" s="8" t="n"/>
-      <c r="AG8" s="8" t="n"/>
-      <c r="AH8" s="8" t="n"/>
-      <c r="AI8" s="8" t="n"/>
-      <c r="AJ8" s="8" t="n"/>
-      <c r="AK8" s="8" t="n"/>
-      <c r="AL8" s="8" t="n"/>
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="9" t="n"/>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="9" t="n"/>
       <c r="AM8" s="9" t="n"/>
       <c r="AN8" s="9" t="n"/>
       <c r="AO8" s="9" t="n"/>
       <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="9" t="n"/>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="9" t="n"/>
-      <c r="AV8" s="9" t="n"/>
+      <c r="AQ8" s="1" t="n"/>
+      <c r="AR8" s="1" t="n"/>
+      <c r="AS8" s="1" t="n"/>
+      <c r="AT8" s="1" t="n"/>
+      <c r="AU8" s="1" t="n"/>
+      <c r="AV8" s="1" t="n"/>
       <c r="AW8" s="1" t="n"/>
       <c r="AX8" s="1" t="n"/>
       <c r="AY8" s="1" t="n"/>
       <c r="AZ8" s="1" t="n"/>
-      <c r="BA8" s="1" t="n"/>
-      <c r="BB8" s="1" t="n"/>
-      <c r="BC8" s="1" t="n"/>
-      <c r="BD8" s="1" t="n"/>
-      <c r="BE8" s="1" t="n"/>
-      <c r="BF8" s="1" t="n"/>
+      <c r="BA8" s="2" t="n"/>
+      <c r="BB8" s="2" t="n"/>
+      <c r="BC8" s="2" t="n"/>
+      <c r="BD8" s="2" t="n"/>
+      <c r="BE8" s="2" t="n"/>
+      <c r="BF8" s="2" t="n"/>
       <c r="BG8" s="2" t="n"/>
       <c r="BH8" s="2" t="n"/>
       <c r="BI8" s="2" t="n"/>
       <c r="BJ8" s="2" t="n"/>
-      <c r="BK8" s="2" t="n"/>
-      <c r="BL8" s="2" t="n"/>
-      <c r="BM8" s="2" t="n"/>
-      <c r="BN8" s="2" t="n"/>
-      <c r="BO8" s="2" t="n"/>
-      <c r="BP8" s="2" t="n"/>
+      <c r="BK8" s="3" t="n"/>
+      <c r="BL8" s="3" t="n"/>
+      <c r="BM8" s="3" t="n"/>
+      <c r="BN8" s="3" t="n"/>
+      <c r="BO8" s="3" t="n"/>
+      <c r="BP8" s="3" t="n"/>
       <c r="BQ8" s="3" t="n"/>
       <c r="BR8" s="3" t="n"/>
       <c r="BS8" s="3" t="n"/>
       <c r="BT8" s="3" t="n"/>
-      <c r="BU8" s="3" t="n"/>
-      <c r="BV8" s="3" t="n"/>
-      <c r="BW8" s="3" t="n"/>
-      <c r="BX8" s="3" t="n"/>
-      <c r="BY8" s="3" t="n"/>
-      <c r="BZ8" s="3" t="n"/>
+      <c r="BU8" s="4" t="n"/>
+      <c r="BV8" s="4" t="n"/>
+      <c r="BW8" s="4" t="n"/>
+      <c r="BX8" s="4" t="n"/>
+      <c r="BY8" s="4" t="n"/>
+      <c r="BZ8" s="4" t="n"/>
       <c r="CA8" s="4" t="n"/>
       <c r="CB8" s="4" t="n"/>
       <c r="CC8" s="4" t="n"/>
       <c r="CD8" s="4" t="n"/>
-      <c r="CE8" s="4" t="n"/>
-      <c r="CF8" s="4" t="n"/>
-      <c r="CG8" s="4" t="n"/>
-      <c r="CH8" s="4" t="n"/>
-      <c r="CI8" s="4" t="n"/>
-      <c r="CJ8" s="4" t="n"/>
+      <c r="CE8" s="5" t="n"/>
+      <c r="CF8" s="5" t="n"/>
+      <c r="CG8" s="5" t="n"/>
+      <c r="CH8" s="5" t="n"/>
+      <c r="CI8" s="5" t="n"/>
+      <c r="CJ8" s="5" t="n"/>
       <c r="CK8" s="5" t="n"/>
       <c r="CL8" s="5" t="n"/>
       <c r="CM8" s="5" t="n"/>
@@ -1340,106 +1340,106 @@
           <t>Maszyna 8</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="6" t="n"/>
-      <c r="Y9" s="6" t="n"/>
-      <c r="Z9" s="6" t="n"/>
-      <c r="AA9" s="6" t="n"/>
-      <c r="AB9" s="6" t="n"/>
-      <c r="AC9" s="6" t="n"/>
-      <c r="AD9" s="6" t="n"/>
-      <c r="AE9" s="6" t="n"/>
-      <c r="AF9" s="6" t="n"/>
-      <c r="AG9" s="6" t="n"/>
-      <c r="AH9" s="7" t="n"/>
-      <c r="AI9" s="7" t="n"/>
-      <c r="AJ9" s="7" t="n"/>
-      <c r="AK9" s="7" t="n"/>
-      <c r="AL9" s="7" t="n"/>
-      <c r="AM9" s="7" t="n"/>
-      <c r="AN9" s="7" t="n"/>
-      <c r="AO9" s="7" t="n"/>
-      <c r="AP9" s="7" t="n"/>
-      <c r="AQ9" s="7" t="n"/>
-      <c r="AR9" s="8" t="n"/>
-      <c r="AS9" s="8" t="n"/>
-      <c r="AT9" s="8" t="n"/>
-      <c r="AU9" s="8" t="n"/>
-      <c r="AV9" s="8" t="n"/>
-      <c r="AW9" s="8" t="n"/>
-      <c r="AX9" s="8" t="n"/>
-      <c r="AY9" s="8" t="n"/>
-      <c r="AZ9" s="8" t="n"/>
-      <c r="BA9" s="8" t="n"/>
-      <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="9" t="n"/>
-      <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n"/>
-      <c r="BG9" s="9" t="n"/>
-      <c r="BH9" s="9" t="n"/>
-      <c r="BI9" s="9" t="n"/>
-      <c r="BJ9" s="9" t="n"/>
-      <c r="BK9" s="9" t="n"/>
-      <c r="BL9" s="1" t="n"/>
-      <c r="BM9" s="1" t="n"/>
-      <c r="BN9" s="1" t="n"/>
-      <c r="BO9" s="1" t="n"/>
-      <c r="BP9" s="1" t="n"/>
-      <c r="BQ9" s="1" t="n"/>
-      <c r="BR9" s="1" t="n"/>
-      <c r="BS9" s="1" t="n"/>
-      <c r="BT9" s="1" t="n"/>
-      <c r="BU9" s="1" t="n"/>
-      <c r="BV9" s="2" t="n"/>
-      <c r="BW9" s="2" t="n"/>
-      <c r="BX9" s="2" t="n"/>
-      <c r="BY9" s="2" t="n"/>
-      <c r="BZ9" s="2" t="n"/>
-      <c r="CA9" s="2" t="n"/>
-      <c r="CB9" s="2" t="n"/>
-      <c r="CC9" s="2" t="n"/>
-      <c r="CD9" s="2" t="n"/>
-      <c r="CE9" s="2" t="n"/>
-      <c r="CF9" s="3" t="n"/>
-      <c r="CG9" s="3" t="n"/>
-      <c r="CH9" s="3" t="n"/>
-      <c r="CI9" s="3" t="n"/>
-      <c r="CJ9" s="3" t="n"/>
-      <c r="CK9" s="3" t="n"/>
-      <c r="CL9" s="3" t="n"/>
-      <c r="CM9" s="3" t="n"/>
-      <c r="CN9" s="3" t="n"/>
-      <c r="CO9" s="3" t="n"/>
-      <c r="CP9" s="3" t="n"/>
-      <c r="CQ9" s="3" t="n"/>
-      <c r="CR9" s="3" t="n"/>
-      <c r="CS9" s="3" t="n"/>
-      <c r="CT9" s="3" t="n"/>
-      <c r="CU9" s="3" t="n"/>
-      <c r="CV9" s="3" t="n"/>
-      <c r="CW9" s="3" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="7" t="n"/>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
+      <c r="W9" s="7" t="n"/>
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="7" t="n"/>
+      <c r="Z9" s="7" t="n"/>
+      <c r="AA9" s="7" t="n"/>
+      <c r="AB9" s="7" t="n"/>
+      <c r="AC9" s="8" t="n"/>
+      <c r="AD9" s="8" t="n"/>
+      <c r="AE9" s="8" t="n"/>
+      <c r="AF9" s="8" t="n"/>
+      <c r="AG9" s="8" t="n"/>
+      <c r="AH9" s="8" t="n"/>
+      <c r="AI9" s="8" t="n"/>
+      <c r="AJ9" s="8" t="n"/>
+      <c r="AK9" s="8" t="n"/>
+      <c r="AL9" s="8" t="n"/>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="9" t="n"/>
+      <c r="AP9" s="9" t="n"/>
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="9" t="n"/>
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="9" t="n"/>
+      <c r="AV9" s="9" t="n"/>
+      <c r="AW9" s="1" t="n"/>
+      <c r="AX9" s="1" t="n"/>
+      <c r="AY9" s="1" t="n"/>
+      <c r="AZ9" s="1" t="n"/>
+      <c r="BA9" s="1" t="n"/>
+      <c r="BB9" s="1" t="n"/>
+      <c r="BC9" s="1" t="n"/>
+      <c r="BD9" s="1" t="n"/>
+      <c r="BE9" s="1" t="n"/>
+      <c r="BF9" s="1" t="n"/>
+      <c r="BG9" s="2" t="n"/>
+      <c r="BH9" s="2" t="n"/>
+      <c r="BI9" s="2" t="n"/>
+      <c r="BJ9" s="2" t="n"/>
+      <c r="BK9" s="2" t="n"/>
+      <c r="BL9" s="2" t="n"/>
+      <c r="BM9" s="2" t="n"/>
+      <c r="BN9" s="2" t="n"/>
+      <c r="BO9" s="2" t="n"/>
+      <c r="BP9" s="2" t="n"/>
+      <c r="BQ9" s="3" t="n"/>
+      <c r="BR9" s="3" t="n"/>
+      <c r="BS9" s="3" t="n"/>
+      <c r="BT9" s="3" t="n"/>
+      <c r="BU9" s="3" t="n"/>
+      <c r="BV9" s="3" t="n"/>
+      <c r="BW9" s="3" t="n"/>
+      <c r="BX9" s="3" t="n"/>
+      <c r="BY9" s="3" t="n"/>
+      <c r="BZ9" s="3" t="n"/>
+      <c r="CA9" s="4" t="n"/>
+      <c r="CB9" s="4" t="n"/>
+      <c r="CC9" s="4" t="n"/>
+      <c r="CD9" s="4" t="n"/>
+      <c r="CE9" s="4" t="n"/>
+      <c r="CF9" s="4" t="n"/>
+      <c r="CG9" s="4" t="n"/>
+      <c r="CH9" s="4" t="n"/>
+      <c r="CI9" s="4" t="n"/>
+      <c r="CJ9" s="4" t="n"/>
+      <c r="CK9" s="5" t="n"/>
+      <c r="CL9" s="5" t="n"/>
+      <c r="CM9" s="5" t="n"/>
+      <c r="CN9" s="5" t="n"/>
+      <c r="CO9" s="5" t="n"/>
+      <c r="CP9" s="5" t="n"/>
+      <c r="CQ9" s="5" t="n"/>
+      <c r="CR9" s="5" t="n"/>
+      <c r="CS9" s="5" t="n"/>
+      <c r="CT9" s="5" t="n"/>
+      <c r="CU9" s="5" t="n"/>
+      <c r="CV9" s="5" t="n"/>
+      <c r="CW9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="10" t="n">
@@ -1744,6 +1744,85 @@
       </c>
       <c r="CX10" s="10" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Zadania:</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Zadanie 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Zadanie 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Zadanie 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Zadanie 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Zadanie 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Zadanie 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Zadanie 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Zadanie 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Zadanie 9</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/harmonogram.xlsx
+++ b/harmonogram.xlsx
@@ -35,20 +35,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0000FF11"/>
+        <bgColor rgb="0000FF11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00858B83"/>
+        <bgColor rgb="00858B83"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0000DBFF"/>
         <bgColor rgb="0000DBFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00004EFF"/>
-        <bgColor rgb="00004EFF"/>
+        <fgColor rgb="00BA4EFF"/>
+        <bgColor rgb="00BA4EFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00858B83"/>
-        <bgColor rgb="00858B83"/>
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00004EFF"/>
+        <bgColor rgb="00004EFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -61,24 +79,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F88100"/>
         <bgColor rgb="00F88100"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BA4EFF"/>
-        <bgColor rgb="00BA4EFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000FF11"/>
-        <bgColor rgb="0000FF11"/>
       </patternFill>
     </fill>
     <fill>
@@ -479,9 +479,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:CX20"/>
+  <dimension ref="A2:CX27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="3" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
     <col width="3" customWidth="1" min="4" max="4"/>
@@ -691,118 +692,12 @@
       <c r="CU2" s="9" t="n"/>
       <c r="CV2" s="9" t="n"/>
       <c r="CW2" s="9" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Maszyna 2</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="4" t="n"/>
-      <c r="R3" s="5" t="n"/>
-      <c r="S3" s="5" t="n"/>
-      <c r="T3" s="5" t="n"/>
-      <c r="U3" s="5" t="n"/>
-      <c r="V3" s="5" t="n"/>
-      <c r="W3" s="5" t="n"/>
-      <c r="X3" s="5" t="n"/>
-      <c r="Y3" s="5" t="n"/>
-      <c r="Z3" s="5" t="n"/>
-      <c r="AA3" s="5" t="n"/>
-      <c r="AB3" s="6" t="n"/>
-      <c r="AC3" s="6" t="n"/>
-      <c r="AD3" s="6" t="n"/>
-      <c r="AE3" s="6" t="n"/>
-      <c r="AF3" s="6" t="n"/>
-      <c r="AG3" s="6" t="n"/>
-      <c r="AH3" s="6" t="n"/>
-      <c r="AI3" s="6" t="n"/>
-      <c r="AJ3" s="6" t="n"/>
-      <c r="AK3" s="6" t="n"/>
-      <c r="AL3" s="7" t="n"/>
-      <c r="AM3" s="7" t="n"/>
-      <c r="AN3" s="7" t="n"/>
-      <c r="AO3" s="7" t="n"/>
-      <c r="AP3" s="7" t="n"/>
-      <c r="AQ3" s="7" t="n"/>
-      <c r="AR3" s="7" t="n"/>
-      <c r="AS3" s="7" t="n"/>
-      <c r="AT3" s="7" t="n"/>
-      <c r="AU3" s="7" t="n"/>
-      <c r="AV3" s="8" t="n"/>
-      <c r="AW3" s="8" t="n"/>
-      <c r="AX3" s="8" t="n"/>
-      <c r="AY3" s="8" t="n"/>
-      <c r="AZ3" s="8" t="n"/>
-      <c r="BA3" s="8" t="n"/>
-      <c r="BB3" s="8" t="n"/>
-      <c r="BC3" s="8" t="n"/>
-      <c r="BD3" s="8" t="n"/>
-      <c r="BE3" s="8" t="n"/>
-      <c r="BF3" s="9" t="n"/>
-      <c r="BG3" s="9" t="n"/>
-      <c r="BH3" s="9" t="n"/>
-      <c r="BI3" s="9" t="n"/>
-      <c r="BJ3" s="9" t="n"/>
-      <c r="BK3" s="9" t="n"/>
-      <c r="BL3" s="9" t="n"/>
-      <c r="BM3" s="9" t="n"/>
-      <c r="BN3" s="9" t="n"/>
-      <c r="BO3" s="9" t="n"/>
-      <c r="BP3" s="1" t="n"/>
-      <c r="BQ3" s="1" t="n"/>
-      <c r="BR3" s="1" t="n"/>
-      <c r="BS3" s="1" t="n"/>
-      <c r="BT3" s="1" t="n"/>
-      <c r="BU3" s="1" t="n"/>
-      <c r="BV3" s="1" t="n"/>
-      <c r="BW3" s="1" t="n"/>
-      <c r="BX3" s="1" t="n"/>
-      <c r="BY3" s="1" t="n"/>
-      <c r="BZ3" s="2" t="n"/>
-      <c r="CA3" s="2" t="n"/>
-      <c r="CB3" s="2" t="n"/>
-      <c r="CC3" s="2" t="n"/>
-      <c r="CD3" s="2" t="n"/>
-      <c r="CE3" s="2" t="n"/>
-      <c r="CF3" s="2" t="n"/>
-      <c r="CG3" s="2" t="n"/>
-      <c r="CH3" s="2" t="n"/>
-      <c r="CI3" s="2" t="n"/>
-      <c r="CJ3" s="3" t="n"/>
-      <c r="CK3" s="3" t="n"/>
-      <c r="CL3" s="3" t="n"/>
-      <c r="CM3" s="3" t="n"/>
-      <c r="CN3" s="3" t="n"/>
-      <c r="CO3" s="3" t="n"/>
-      <c r="CP3" s="3" t="n"/>
-      <c r="CQ3" s="3" t="n"/>
-      <c r="CR3" s="3" t="n"/>
-      <c r="CS3" s="3" t="n"/>
-      <c r="CT3" s="3" t="n"/>
-      <c r="CU3" s="3" t="n"/>
-      <c r="CV3" s="3" t="n"/>
-      <c r="CW3" s="3" t="n"/>
+      <c r="CX2" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maszyna 3</t>
+          <t>Maszyna 2</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -817,80 +712,80 @@
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="4" t="n"/>
       <c r="R4" s="5" t="n"/>
       <c r="S4" s="5" t="n"/>
       <c r="T4" s="5" t="n"/>
       <c r="U4" s="5" t="n"/>
       <c r="V4" s="5" t="n"/>
       <c r="W4" s="5" t="n"/>
-      <c r="X4" s="6" t="n"/>
-      <c r="Y4" s="6" t="n"/>
-      <c r="Z4" s="6" t="n"/>
-      <c r="AA4" s="6" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
       <c r="AB4" s="6" t="n"/>
       <c r="AC4" s="6" t="n"/>
       <c r="AD4" s="6" t="n"/>
       <c r="AE4" s="6" t="n"/>
       <c r="AF4" s="6" t="n"/>
       <c r="AG4" s="6" t="n"/>
-      <c r="AH4" s="7" t="n"/>
-      <c r="AI4" s="7" t="n"/>
-      <c r="AJ4" s="7" t="n"/>
-      <c r="AK4" s="7" t="n"/>
+      <c r="AH4" s="6" t="n"/>
+      <c r="AI4" s="6" t="n"/>
+      <c r="AJ4" s="6" t="n"/>
+      <c r="AK4" s="6" t="n"/>
       <c r="AL4" s="7" t="n"/>
       <c r="AM4" s="7" t="n"/>
       <c r="AN4" s="7" t="n"/>
       <c r="AO4" s="7" t="n"/>
       <c r="AP4" s="7" t="n"/>
       <c r="AQ4" s="7" t="n"/>
-      <c r="AR4" s="8" t="n"/>
-      <c r="AS4" s="8" t="n"/>
-      <c r="AT4" s="8" t="n"/>
-      <c r="AU4" s="8" t="n"/>
+      <c r="AR4" s="7" t="n"/>
+      <c r="AS4" s="7" t="n"/>
+      <c r="AT4" s="7" t="n"/>
+      <c r="AU4" s="7" t="n"/>
       <c r="AV4" s="8" t="n"/>
       <c r="AW4" s="8" t="n"/>
       <c r="AX4" s="8" t="n"/>
       <c r="AY4" s="8" t="n"/>
       <c r="AZ4" s="8" t="n"/>
       <c r="BA4" s="8" t="n"/>
-      <c r="BB4" s="9" t="n"/>
-      <c r="BC4" s="9" t="n"/>
-      <c r="BD4" s="9" t="n"/>
-      <c r="BE4" s="9" t="n"/>
+      <c r="BB4" s="8" t="n"/>
+      <c r="BC4" s="8" t="n"/>
+      <c r="BD4" s="8" t="n"/>
+      <c r="BE4" s="8" t="n"/>
       <c r="BF4" s="9" t="n"/>
       <c r="BG4" s="9" t="n"/>
       <c r="BH4" s="9" t="n"/>
       <c r="BI4" s="9" t="n"/>
       <c r="BJ4" s="9" t="n"/>
       <c r="BK4" s="9" t="n"/>
-      <c r="BL4" s="1" t="n"/>
-      <c r="BM4" s="1" t="n"/>
-      <c r="BN4" s="1" t="n"/>
-      <c r="BO4" s="1" t="n"/>
+      <c r="BL4" s="9" t="n"/>
+      <c r="BM4" s="9" t="n"/>
+      <c r="BN4" s="9" t="n"/>
+      <c r="BO4" s="9" t="n"/>
       <c r="BP4" s="1" t="n"/>
       <c r="BQ4" s="1" t="n"/>
       <c r="BR4" s="1" t="n"/>
       <c r="BS4" s="1" t="n"/>
       <c r="BT4" s="1" t="n"/>
       <c r="BU4" s="1" t="n"/>
-      <c r="BV4" s="2" t="n"/>
-      <c r="BW4" s="2" t="n"/>
-      <c r="BX4" s="2" t="n"/>
-      <c r="BY4" s="2" t="n"/>
+      <c r="BV4" s="1" t="n"/>
+      <c r="BW4" s="1" t="n"/>
+      <c r="BX4" s="1" t="n"/>
+      <c r="BY4" s="1" t="n"/>
       <c r="BZ4" s="2" t="n"/>
       <c r="CA4" s="2" t="n"/>
       <c r="CB4" s="2" t="n"/>
       <c r="CC4" s="2" t="n"/>
       <c r="CD4" s="2" t="n"/>
       <c r="CE4" s="2" t="n"/>
-      <c r="CF4" s="3" t="n"/>
-      <c r="CG4" s="3" t="n"/>
-      <c r="CH4" s="3" t="n"/>
-      <c r="CI4" s="3" t="n"/>
+      <c r="CF4" s="2" t="n"/>
+      <c r="CG4" s="2" t="n"/>
+      <c r="CH4" s="2" t="n"/>
+      <c r="CI4" s="2" t="n"/>
       <c r="CJ4" s="3" t="n"/>
       <c r="CK4" s="3" t="n"/>
       <c r="CL4" s="3" t="n"/>
@@ -905,915 +800,973 @@
       <c r="CU4" s="3" t="n"/>
       <c r="CV4" s="3" t="n"/>
       <c r="CW4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Maszyna 4</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="n"/>
-      <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="n"/>
-      <c r="O5" s="1" t="n"/>
-      <c r="P5" s="1" t="n"/>
-      <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n"/>
-      <c r="T5" s="2" t="n"/>
-      <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="n"/>
-      <c r="W5" s="2" t="n"/>
-      <c r="X5" s="2" t="n"/>
-      <c r="Y5" s="2" t="n"/>
-      <c r="Z5" s="2" t="n"/>
-      <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="3" t="n"/>
-      <c r="AC5" s="3" t="n"/>
-      <c r="AD5" s="3" t="n"/>
-      <c r="AE5" s="3" t="n"/>
-      <c r="AF5" s="3" t="n"/>
-      <c r="AG5" s="3" t="n"/>
-      <c r="AH5" s="3" t="n"/>
-      <c r="AI5" s="3" t="n"/>
-      <c r="AJ5" s="3" t="n"/>
-      <c r="AK5" s="4" t="n"/>
-      <c r="AL5" s="4" t="n"/>
-      <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="n"/>
-      <c r="AO5" s="4" t="n"/>
-      <c r="AP5" s="4" t="n"/>
-      <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="n"/>
-      <c r="AS5" s="4" t="n"/>
-      <c r="AT5" s="4" t="n"/>
-      <c r="AU5" s="5" t="n"/>
-      <c r="AV5" s="5" t="n"/>
-      <c r="AW5" s="5" t="n"/>
-      <c r="AX5" s="5" t="n"/>
-      <c r="AY5" s="5" t="n"/>
-      <c r="AZ5" s="5" t="n"/>
-      <c r="BA5" s="5" t="n"/>
-      <c r="BB5" s="5" t="n"/>
-      <c r="BC5" s="5" t="n"/>
-      <c r="BD5" s="5" t="n"/>
-      <c r="BE5" s="6" t="n"/>
-      <c r="BF5" s="6" t="n"/>
-      <c r="BG5" s="6" t="n"/>
-      <c r="BH5" s="6" t="n"/>
-      <c r="BI5" s="6" t="n"/>
-      <c r="BJ5" s="6" t="n"/>
-      <c r="BK5" s="6" t="n"/>
-      <c r="BL5" s="6" t="n"/>
-      <c r="BM5" s="6" t="n"/>
-      <c r="BN5" s="6" t="n"/>
-      <c r="BO5" s="7" t="n"/>
-      <c r="BP5" s="7" t="n"/>
-      <c r="BQ5" s="7" t="n"/>
-      <c r="BR5" s="7" t="n"/>
-      <c r="BS5" s="7" t="n"/>
-      <c r="BT5" s="7" t="n"/>
-      <c r="BU5" s="7" t="n"/>
-      <c r="BV5" s="7" t="n"/>
-      <c r="BW5" s="7" t="n"/>
-      <c r="BX5" s="7" t="n"/>
-      <c r="BY5" s="8" t="n"/>
-      <c r="BZ5" s="8" t="n"/>
-      <c r="CA5" s="8" t="n"/>
-      <c r="CB5" s="8" t="n"/>
-      <c r="CC5" s="8" t="n"/>
-      <c r="CD5" s="8" t="n"/>
-      <c r="CE5" s="8" t="n"/>
-      <c r="CF5" s="8" t="n"/>
-      <c r="CG5" s="8" t="n"/>
-      <c r="CH5" s="8" t="n"/>
-      <c r="CI5" s="9" t="n"/>
-      <c r="CJ5" s="9" t="n"/>
-      <c r="CK5" s="9" t="n"/>
-      <c r="CL5" s="9" t="n"/>
-      <c r="CM5" s="9" t="n"/>
-      <c r="CN5" s="9" t="n"/>
-      <c r="CO5" s="9" t="n"/>
-      <c r="CP5" s="9" t="n"/>
-      <c r="CQ5" s="9" t="n"/>
-      <c r="CR5" s="9" t="n"/>
-      <c r="CS5" s="9" t="n"/>
-      <c r="CT5" s="9" t="n"/>
-      <c r="CU5" s="9" t="n"/>
-      <c r="CV5" s="9" t="n"/>
-      <c r="CW5" s="9" t="n"/>
+      <c r="CX4" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Maszyna 5</t>
+          <t>Maszyna 3</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="7" t="n"/>
-      <c r="S6" s="7" t="n"/>
-      <c r="T6" s="7" t="n"/>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="8" t="n"/>
-      <c r="AA6" s="8" t="n"/>
-      <c r="AB6" s="8" t="n"/>
-      <c r="AC6" s="8" t="n"/>
-      <c r="AD6" s="8" t="n"/>
-      <c r="AE6" s="8" t="n"/>
-      <c r="AF6" s="8" t="n"/>
-      <c r="AG6" s="8" t="n"/>
-      <c r="AH6" s="8" t="n"/>
-      <c r="AI6" s="8" t="n"/>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="9" t="n"/>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="9" t="n"/>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="9" t="n"/>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="1" t="n"/>
-      <c r="AU6" s="1" t="n"/>
-      <c r="AV6" s="1" t="n"/>
-      <c r="AW6" s="1" t="n"/>
-      <c r="AX6" s="1" t="n"/>
-      <c r="AY6" s="1" t="n"/>
-      <c r="AZ6" s="1" t="n"/>
-      <c r="BA6" s="1" t="n"/>
-      <c r="BB6" s="1" t="n"/>
-      <c r="BC6" s="1" t="n"/>
-      <c r="BD6" s="2" t="n"/>
-      <c r="BE6" s="2" t="n"/>
-      <c r="BF6" s="2" t="n"/>
-      <c r="BG6" s="2" t="n"/>
-      <c r="BH6" s="2" t="n"/>
-      <c r="BI6" s="2" t="n"/>
-      <c r="BJ6" s="2" t="n"/>
-      <c r="BK6" s="2" t="n"/>
-      <c r="BL6" s="2" t="n"/>
-      <c r="BM6" s="2" t="n"/>
-      <c r="BN6" s="3" t="n"/>
-      <c r="BO6" s="3" t="n"/>
-      <c r="BP6" s="3" t="n"/>
-      <c r="BQ6" s="3" t="n"/>
-      <c r="BR6" s="3" t="n"/>
-      <c r="BS6" s="3" t="n"/>
-      <c r="BT6" s="3" t="n"/>
-      <c r="BU6" s="3" t="n"/>
-      <c r="BV6" s="3" t="n"/>
-      <c r="BW6" s="3" t="n"/>
-      <c r="BX6" s="4" t="n"/>
-      <c r="BY6" s="4" t="n"/>
-      <c r="BZ6" s="4" t="n"/>
-      <c r="CA6" s="4" t="n"/>
-      <c r="CB6" s="4" t="n"/>
-      <c r="CC6" s="4" t="n"/>
-      <c r="CD6" s="4" t="n"/>
-      <c r="CE6" s="4" t="n"/>
-      <c r="CF6" s="4" t="n"/>
-      <c r="CG6" s="4" t="n"/>
-      <c r="CH6" s="5" t="n"/>
-      <c r="CI6" s="5" t="n"/>
-      <c r="CJ6" s="5" t="n"/>
-      <c r="CK6" s="5" t="n"/>
-      <c r="CL6" s="5" t="n"/>
-      <c r="CM6" s="5" t="n"/>
-      <c r="CN6" s="5" t="n"/>
-      <c r="CO6" s="5" t="n"/>
-      <c r="CP6" s="5" t="n"/>
-      <c r="CQ6" s="5" t="n"/>
-      <c r="CR6" s="5" t="n"/>
-      <c r="CS6" s="5" t="n"/>
-      <c r="CT6" s="5" t="n"/>
-      <c r="CU6" s="5" t="n"/>
-      <c r="CV6" s="5" t="n"/>
-      <c r="CW6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Maszyna 6</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n"/>
-      <c r="O7" s="8" t="n"/>
-      <c r="P7" s="8" t="n"/>
-      <c r="Q7" s="8" t="n"/>
-      <c r="R7" s="8" t="n"/>
-      <c r="S7" s="8" t="n"/>
-      <c r="T7" s="8" t="n"/>
-      <c r="U7" s="8" t="n"/>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="9" t="n"/>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="9" t="n"/>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="9" t="n"/>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="1" t="n"/>
-      <c r="AG7" s="1" t="n"/>
-      <c r="AH7" s="1" t="n"/>
-      <c r="AI7" s="1" t="n"/>
-      <c r="AJ7" s="1" t="n"/>
-      <c r="AK7" s="1" t="n"/>
-      <c r="AL7" s="1" t="n"/>
-      <c r="AM7" s="1" t="n"/>
-      <c r="AN7" s="1" t="n"/>
-      <c r="AO7" s="1" t="n"/>
-      <c r="AP7" s="2" t="n"/>
-      <c r="AQ7" s="2" t="n"/>
-      <c r="AR7" s="2" t="n"/>
-      <c r="AS7" s="2" t="n"/>
-      <c r="AT7" s="2" t="n"/>
-      <c r="AU7" s="2" t="n"/>
-      <c r="AV7" s="2" t="n"/>
-      <c r="AW7" s="2" t="n"/>
-      <c r="AX7" s="2" t="n"/>
-      <c r="AY7" s="2" t="n"/>
-      <c r="AZ7" s="3" t="n"/>
-      <c r="BA7" s="3" t="n"/>
-      <c r="BB7" s="3" t="n"/>
-      <c r="BC7" s="3" t="n"/>
-      <c r="BD7" s="3" t="n"/>
-      <c r="BE7" s="3" t="n"/>
-      <c r="BF7" s="3" t="n"/>
-      <c r="BG7" s="3" t="n"/>
-      <c r="BH7" s="3" t="n"/>
-      <c r="BI7" s="3" t="n"/>
-      <c r="BJ7" s="4" t="n"/>
-      <c r="BK7" s="4" t="n"/>
-      <c r="BL7" s="4" t="n"/>
-      <c r="BM7" s="4" t="n"/>
-      <c r="BN7" s="4" t="n"/>
-      <c r="BO7" s="4" t="n"/>
-      <c r="BP7" s="4" t="n"/>
-      <c r="BQ7" s="4" t="n"/>
-      <c r="BR7" s="4" t="n"/>
-      <c r="BS7" s="4" t="n"/>
-      <c r="BT7" s="5" t="n"/>
-      <c r="BU7" s="5" t="n"/>
-      <c r="BV7" s="5" t="n"/>
-      <c r="BW7" s="5" t="n"/>
-      <c r="BX7" s="5" t="n"/>
-      <c r="BY7" s="5" t="n"/>
-      <c r="BZ7" s="5" t="n"/>
-      <c r="CA7" s="5" t="n"/>
-      <c r="CB7" s="5" t="n"/>
-      <c r="CC7" s="5" t="n"/>
-      <c r="CD7" s="6" t="n"/>
-      <c r="CE7" s="6" t="n"/>
-      <c r="CF7" s="6" t="n"/>
-      <c r="CG7" s="6" t="n"/>
-      <c r="CH7" s="6" t="n"/>
-      <c r="CI7" s="6" t="n"/>
-      <c r="CJ7" s="6" t="n"/>
-      <c r="CK7" s="6" t="n"/>
-      <c r="CL7" s="6" t="n"/>
-      <c r="CM7" s="6" t="n"/>
-      <c r="CN7" s="6" t="n"/>
-      <c r="CO7" s="6" t="n"/>
-      <c r="CP7" s="6" t="n"/>
-      <c r="CQ7" s="6" t="n"/>
-      <c r="CR7" s="6" t="n"/>
-      <c r="CS7" s="6" t="n"/>
-      <c r="CT7" s="6" t="n"/>
-      <c r="CU7" s="6" t="n"/>
-      <c r="CV7" s="6" t="n"/>
-      <c r="CW7" s="6" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="8" t="n"/>
+      <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="8" t="n"/>
+      <c r="T6" s="8" t="n"/>
+      <c r="U6" s="8" t="n"/>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="9" t="n"/>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="9" t="n"/>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="9" t="n"/>
+      <c r="AD6" s="9" t="n"/>
+      <c r="AE6" s="9" t="n"/>
+      <c r="AF6" s="1" t="n"/>
+      <c r="AG6" s="1" t="n"/>
+      <c r="AH6" s="1" t="n"/>
+      <c r="AI6" s="1" t="n"/>
+      <c r="AJ6" s="1" t="n"/>
+      <c r="AK6" s="1" t="n"/>
+      <c r="AL6" s="1" t="n"/>
+      <c r="AM6" s="1" t="n"/>
+      <c r="AN6" s="1" t="n"/>
+      <c r="AO6" s="1" t="n"/>
+      <c r="AP6" s="2" t="n"/>
+      <c r="AQ6" s="2" t="n"/>
+      <c r="AR6" s="2" t="n"/>
+      <c r="AS6" s="2" t="n"/>
+      <c r="AT6" s="2" t="n"/>
+      <c r="AU6" s="2" t="n"/>
+      <c r="AV6" s="2" t="n"/>
+      <c r="AW6" s="2" t="n"/>
+      <c r="AX6" s="2" t="n"/>
+      <c r="AY6" s="2" t="n"/>
+      <c r="AZ6" s="3" t="n"/>
+      <c r="BA6" s="3" t="n"/>
+      <c r="BB6" s="3" t="n"/>
+      <c r="BC6" s="3" t="n"/>
+      <c r="BD6" s="3" t="n"/>
+      <c r="BE6" s="3" t="n"/>
+      <c r="BF6" s="3" t="n"/>
+      <c r="BG6" s="3" t="n"/>
+      <c r="BH6" s="3" t="n"/>
+      <c r="BI6" s="3" t="n"/>
+      <c r="BJ6" s="4" t="n"/>
+      <c r="BK6" s="4" t="n"/>
+      <c r="BL6" s="4" t="n"/>
+      <c r="BM6" s="4" t="n"/>
+      <c r="BN6" s="4" t="n"/>
+      <c r="BO6" s="4" t="n"/>
+      <c r="BP6" s="4" t="n"/>
+      <c r="BQ6" s="4" t="n"/>
+      <c r="BR6" s="4" t="n"/>
+      <c r="BS6" s="4" t="n"/>
+      <c r="BT6" s="5" t="n"/>
+      <c r="BU6" s="5" t="n"/>
+      <c r="BV6" s="5" t="n"/>
+      <c r="BW6" s="5" t="n"/>
+      <c r="BX6" s="5" t="n"/>
+      <c r="BY6" s="5" t="n"/>
+      <c r="BZ6" s="5" t="n"/>
+      <c r="CA6" s="5" t="n"/>
+      <c r="CB6" s="5" t="n"/>
+      <c r="CC6" s="5" t="n"/>
+      <c r="CD6" s="6" t="n"/>
+      <c r="CE6" s="6" t="n"/>
+      <c r="CF6" s="6" t="n"/>
+      <c r="CG6" s="6" t="n"/>
+      <c r="CH6" s="6" t="n"/>
+      <c r="CI6" s="6" t="n"/>
+      <c r="CJ6" s="6" t="n"/>
+      <c r="CK6" s="6" t="n"/>
+      <c r="CL6" s="6" t="n"/>
+      <c r="CM6" s="6" t="n"/>
+      <c r="CN6" s="6" t="n"/>
+      <c r="CO6" s="6" t="n"/>
+      <c r="CP6" s="6" t="n"/>
+      <c r="CQ6" s="6" t="n"/>
+      <c r="CR6" s="6" t="n"/>
+      <c r="CS6" s="6" t="n"/>
+      <c r="CT6" s="6" t="n"/>
+      <c r="CU6" s="6" t="n"/>
+      <c r="CV6" s="6" t="n"/>
+      <c r="CW6" s="6" t="n"/>
+      <c r="CX6" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Maszyna 4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
+      <c r="Z8" s="6" t="n"/>
+      <c r="AA8" s="6" t="n"/>
+      <c r="AB8" s="6" t="n"/>
+      <c r="AC8" s="6" t="n"/>
+      <c r="AD8" s="6" t="n"/>
+      <c r="AE8" s="6" t="n"/>
+      <c r="AF8" s="6" t="n"/>
+      <c r="AG8" s="6" t="n"/>
+      <c r="AH8" s="7" t="n"/>
+      <c r="AI8" s="7" t="n"/>
+      <c r="AJ8" s="7" t="n"/>
+      <c r="AK8" s="7" t="n"/>
+      <c r="AL8" s="7" t="n"/>
+      <c r="AM8" s="7" t="n"/>
+      <c r="AN8" s="7" t="n"/>
+      <c r="AO8" s="7" t="n"/>
+      <c r="AP8" s="7" t="n"/>
+      <c r="AQ8" s="7" t="n"/>
+      <c r="AR8" s="8" t="n"/>
+      <c r="AS8" s="8" t="n"/>
+      <c r="AT8" s="8" t="n"/>
+      <c r="AU8" s="8" t="n"/>
+      <c r="AV8" s="8" t="n"/>
+      <c r="AW8" s="8" t="n"/>
+      <c r="AX8" s="8" t="n"/>
+      <c r="AY8" s="8" t="n"/>
+      <c r="AZ8" s="8" t="n"/>
+      <c r="BA8" s="8" t="n"/>
+      <c r="BB8" s="9" t="n"/>
+      <c r="BC8" s="9" t="n"/>
+      <c r="BD8" s="9" t="n"/>
+      <c r="BE8" s="9" t="n"/>
+      <c r="BF8" s="9" t="n"/>
+      <c r="BG8" s="9" t="n"/>
+      <c r="BH8" s="9" t="n"/>
+      <c r="BI8" s="9" t="n"/>
+      <c r="BJ8" s="9" t="n"/>
+      <c r="BK8" s="9" t="n"/>
+      <c r="BL8" s="1" t="n"/>
+      <c r="BM8" s="1" t="n"/>
+      <c r="BN8" s="1" t="n"/>
+      <c r="BO8" s="1" t="n"/>
+      <c r="BP8" s="1" t="n"/>
+      <c r="BQ8" s="1" t="n"/>
+      <c r="BR8" s="1" t="n"/>
+      <c r="BS8" s="1" t="n"/>
+      <c r="BT8" s="1" t="n"/>
+      <c r="BU8" s="1" t="n"/>
+      <c r="BV8" s="2" t="n"/>
+      <c r="BW8" s="2" t="n"/>
+      <c r="BX8" s="2" t="n"/>
+      <c r="BY8" s="2" t="n"/>
+      <c r="BZ8" s="2" t="n"/>
+      <c r="CA8" s="2" t="n"/>
+      <c r="CB8" s="2" t="n"/>
+      <c r="CC8" s="2" t="n"/>
+      <c r="CD8" s="2" t="n"/>
+      <c r="CE8" s="2" t="n"/>
+      <c r="CF8" s="3" t="n"/>
+      <c r="CG8" s="3" t="n"/>
+      <c r="CH8" s="3" t="n"/>
+      <c r="CI8" s="3" t="n"/>
+      <c r="CJ8" s="3" t="n"/>
+      <c r="CK8" s="3" t="n"/>
+      <c r="CL8" s="3" t="n"/>
+      <c r="CM8" s="3" t="n"/>
+      <c r="CN8" s="3" t="n"/>
+      <c r="CO8" s="3" t="n"/>
+      <c r="CP8" s="3" t="n"/>
+      <c r="CQ8" s="3" t="n"/>
+      <c r="CR8" s="3" t="n"/>
+      <c r="CS8" s="3" t="n"/>
+      <c r="CT8" s="3" t="n"/>
+      <c r="CU8" s="3" t="n"/>
+      <c r="CV8" s="3" t="n"/>
+      <c r="CW8" s="3" t="n"/>
+      <c r="CX8" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Maszyna 5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
+      <c r="O10" s="7" t="n"/>
+      <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="7" t="n"/>
+      <c r="T10" s="7" t="n"/>
+      <c r="U10" s="7" t="n"/>
+      <c r="V10" s="7" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="9" t="n"/>
+      <c r="AH10" s="9" t="n"/>
+      <c r="AI10" s="9" t="n"/>
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="9" t="n"/>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="9" t="n"/>
+      <c r="AP10" s="9" t="n"/>
+      <c r="AQ10" s="1" t="n"/>
+      <c r="AR10" s="1" t="n"/>
+      <c r="AS10" s="1" t="n"/>
+      <c r="AT10" s="1" t="n"/>
+      <c r="AU10" s="1" t="n"/>
+      <c r="AV10" s="1" t="n"/>
+      <c r="AW10" s="1" t="n"/>
+      <c r="AX10" s="1" t="n"/>
+      <c r="AY10" s="1" t="n"/>
+      <c r="AZ10" s="1" t="n"/>
+      <c r="BA10" s="2" t="n"/>
+      <c r="BB10" s="2" t="n"/>
+      <c r="BC10" s="2" t="n"/>
+      <c r="BD10" s="2" t="n"/>
+      <c r="BE10" s="2" t="n"/>
+      <c r="BF10" s="2" t="n"/>
+      <c r="BG10" s="2" t="n"/>
+      <c r="BH10" s="2" t="n"/>
+      <c r="BI10" s="2" t="n"/>
+      <c r="BJ10" s="2" t="n"/>
+      <c r="BK10" s="3" t="n"/>
+      <c r="BL10" s="3" t="n"/>
+      <c r="BM10" s="3" t="n"/>
+      <c r="BN10" s="3" t="n"/>
+      <c r="BO10" s="3" t="n"/>
+      <c r="BP10" s="3" t="n"/>
+      <c r="BQ10" s="3" t="n"/>
+      <c r="BR10" s="3" t="n"/>
+      <c r="BS10" s="3" t="n"/>
+      <c r="BT10" s="3" t="n"/>
+      <c r="BU10" s="4" t="n"/>
+      <c r="BV10" s="4" t="n"/>
+      <c r="BW10" s="4" t="n"/>
+      <c r="BX10" s="4" t="n"/>
+      <c r="BY10" s="4" t="n"/>
+      <c r="BZ10" s="4" t="n"/>
+      <c r="CA10" s="4" t="n"/>
+      <c r="CB10" s="4" t="n"/>
+      <c r="CC10" s="4" t="n"/>
+      <c r="CD10" s="4" t="n"/>
+      <c r="CE10" s="5" t="n"/>
+      <c r="CF10" s="5" t="n"/>
+      <c r="CG10" s="5" t="n"/>
+      <c r="CH10" s="5" t="n"/>
+      <c r="CI10" s="5" t="n"/>
+      <c r="CJ10" s="5" t="n"/>
+      <c r="CK10" s="5" t="n"/>
+      <c r="CL10" s="5" t="n"/>
+      <c r="CM10" s="5" t="n"/>
+      <c r="CN10" s="5" t="n"/>
+      <c r="CO10" s="5" t="n"/>
+      <c r="CP10" s="5" t="n"/>
+      <c r="CQ10" s="5" t="n"/>
+      <c r="CR10" s="5" t="n"/>
+      <c r="CS10" s="5" t="n"/>
+      <c r="CT10" s="5" t="n"/>
+      <c r="CU10" s="5" t="n"/>
+      <c r="CV10" s="5" t="n"/>
+      <c r="CW10" s="5" t="n"/>
+      <c r="CX10" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Maszyna 6</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
+      <c r="M12" s="1" t="n"/>
+      <c r="N12" s="1" t="n"/>
+      <c r="O12" s="1" t="n"/>
+      <c r="P12" s="1" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="W12" s="2" t="n"/>
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="2" t="n"/>
+      <c r="Z12" s="2" t="n"/>
+      <c r="AA12" s="3" t="n"/>
+      <c r="AB12" s="3" t="n"/>
+      <c r="AC12" s="3" t="n"/>
+      <c r="AD12" s="3" t="n"/>
+      <c r="AE12" s="3" t="n"/>
+      <c r="AF12" s="3" t="n"/>
+      <c r="AG12" s="3" t="n"/>
+      <c r="AH12" s="3" t="n"/>
+      <c r="AI12" s="3" t="n"/>
+      <c r="AJ12" s="3" t="n"/>
+      <c r="AK12" s="4" t="n"/>
+      <c r="AL12" s="4" t="n"/>
+      <c r="AM12" s="4" t="n"/>
+      <c r="AN12" s="4" t="n"/>
+      <c r="AO12" s="4" t="n"/>
+      <c r="AP12" s="4" t="n"/>
+      <c r="AQ12" s="4" t="n"/>
+      <c r="AR12" s="4" t="n"/>
+      <c r="AS12" s="4" t="n"/>
+      <c r="AT12" s="4" t="n"/>
+      <c r="AU12" s="5" t="n"/>
+      <c r="AV12" s="5" t="n"/>
+      <c r="AW12" s="5" t="n"/>
+      <c r="AX12" s="5" t="n"/>
+      <c r="AY12" s="5" t="n"/>
+      <c r="AZ12" s="5" t="n"/>
+      <c r="BA12" s="5" t="n"/>
+      <c r="BB12" s="5" t="n"/>
+      <c r="BC12" s="5" t="n"/>
+      <c r="BD12" s="5" t="n"/>
+      <c r="BE12" s="6" t="n"/>
+      <c r="BF12" s="6" t="n"/>
+      <c r="BG12" s="6" t="n"/>
+      <c r="BH12" s="6" t="n"/>
+      <c r="BI12" s="6" t="n"/>
+      <c r="BJ12" s="6" t="n"/>
+      <c r="BK12" s="6" t="n"/>
+      <c r="BL12" s="6" t="n"/>
+      <c r="BM12" s="6" t="n"/>
+      <c r="BN12" s="6" t="n"/>
+      <c r="BO12" s="7" t="n"/>
+      <c r="BP12" s="7" t="n"/>
+      <c r="BQ12" s="7" t="n"/>
+      <c r="BR12" s="7" t="n"/>
+      <c r="BS12" s="7" t="n"/>
+      <c r="BT12" s="7" t="n"/>
+      <c r="BU12" s="7" t="n"/>
+      <c r="BV12" s="7" t="n"/>
+      <c r="BW12" s="7" t="n"/>
+      <c r="BX12" s="7" t="n"/>
+      <c r="BY12" s="8" t="n"/>
+      <c r="BZ12" s="8" t="n"/>
+      <c r="CA12" s="8" t="n"/>
+      <c r="CB12" s="8" t="n"/>
+      <c r="CC12" s="8" t="n"/>
+      <c r="CD12" s="8" t="n"/>
+      <c r="CE12" s="8" t="n"/>
+      <c r="CF12" s="8" t="n"/>
+      <c r="CG12" s="8" t="n"/>
+      <c r="CH12" s="8" t="n"/>
+      <c r="CI12" s="9" t="n"/>
+      <c r="CJ12" s="9" t="n"/>
+      <c r="CK12" s="9" t="n"/>
+      <c r="CL12" s="9" t="n"/>
+      <c r="CM12" s="9" t="n"/>
+      <c r="CN12" s="9" t="n"/>
+      <c r="CO12" s="9" t="n"/>
+      <c r="CP12" s="9" t="n"/>
+      <c r="CQ12" s="9" t="n"/>
+      <c r="CR12" s="9" t="n"/>
+      <c r="CS12" s="9" t="n"/>
+      <c r="CT12" s="9" t="n"/>
+      <c r="CU12" s="9" t="n"/>
+      <c r="CV12" s="9" t="n"/>
+      <c r="CW12" s="9" t="n"/>
+      <c r="CX12" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Maszyna 7</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="7" t="n"/>
-      <c r="S8" s="7" t="n"/>
-      <c r="T8" s="7" t="n"/>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="8" t="n"/>
-      <c r="X8" s="8" t="n"/>
-      <c r="Y8" s="8" t="n"/>
-      <c r="Z8" s="8" t="n"/>
-      <c r="AA8" s="8" t="n"/>
-      <c r="AB8" s="8" t="n"/>
-      <c r="AC8" s="8" t="n"/>
-      <c r="AD8" s="8" t="n"/>
-      <c r="AE8" s="8" t="n"/>
-      <c r="AF8" s="8" t="n"/>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="9" t="n"/>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="9" t="n"/>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="9" t="n"/>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="1" t="n"/>
-      <c r="AR8" s="1" t="n"/>
-      <c r="AS8" s="1" t="n"/>
-      <c r="AT8" s="1" t="n"/>
-      <c r="AU8" s="1" t="n"/>
-      <c r="AV8" s="1" t="n"/>
-      <c r="AW8" s="1" t="n"/>
-      <c r="AX8" s="1" t="n"/>
-      <c r="AY8" s="1" t="n"/>
-      <c r="AZ8" s="1" t="n"/>
-      <c r="BA8" s="2" t="n"/>
-      <c r="BB8" s="2" t="n"/>
-      <c r="BC8" s="2" t="n"/>
-      <c r="BD8" s="2" t="n"/>
-      <c r="BE8" s="2" t="n"/>
-      <c r="BF8" s="2" t="n"/>
-      <c r="BG8" s="2" t="n"/>
-      <c r="BH8" s="2" t="n"/>
-      <c r="BI8" s="2" t="n"/>
-      <c r="BJ8" s="2" t="n"/>
-      <c r="BK8" s="3" t="n"/>
-      <c r="BL8" s="3" t="n"/>
-      <c r="BM8" s="3" t="n"/>
-      <c r="BN8" s="3" t="n"/>
-      <c r="BO8" s="3" t="n"/>
-      <c r="BP8" s="3" t="n"/>
-      <c r="BQ8" s="3" t="n"/>
-      <c r="BR8" s="3" t="n"/>
-      <c r="BS8" s="3" t="n"/>
-      <c r="BT8" s="3" t="n"/>
-      <c r="BU8" s="4" t="n"/>
-      <c r="BV8" s="4" t="n"/>
-      <c r="BW8" s="4" t="n"/>
-      <c r="BX8" s="4" t="n"/>
-      <c r="BY8" s="4" t="n"/>
-      <c r="BZ8" s="4" t="n"/>
-      <c r="CA8" s="4" t="n"/>
-      <c r="CB8" s="4" t="n"/>
-      <c r="CC8" s="4" t="n"/>
-      <c r="CD8" s="4" t="n"/>
-      <c r="CE8" s="5" t="n"/>
-      <c r="CF8" s="5" t="n"/>
-      <c r="CG8" s="5" t="n"/>
-      <c r="CH8" s="5" t="n"/>
-      <c r="CI8" s="5" t="n"/>
-      <c r="CJ8" s="5" t="n"/>
-      <c r="CK8" s="5" t="n"/>
-      <c r="CL8" s="5" t="n"/>
-      <c r="CM8" s="5" t="n"/>
-      <c r="CN8" s="5" t="n"/>
-      <c r="CO8" s="5" t="n"/>
-      <c r="CP8" s="5" t="n"/>
-      <c r="CQ8" s="5" t="n"/>
-      <c r="CR8" s="5" t="n"/>
-      <c r="CS8" s="5" t="n"/>
-      <c r="CT8" s="5" t="n"/>
-      <c r="CU8" s="5" t="n"/>
-      <c r="CV8" s="5" t="n"/>
-      <c r="CW8" s="5" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="7" t="n"/>
+      <c r="T14" s="7" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="n"/>
+      <c r="Y14" s="7" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8" t="n"/>
+      <c r="AI14" s="8" t="n"/>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="9" t="n"/>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="9" t="n"/>
+      <c r="AP14" s="9" t="n"/>
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="9" t="n"/>
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="1" t="n"/>
+      <c r="AU14" s="1" t="n"/>
+      <c r="AV14" s="1" t="n"/>
+      <c r="AW14" s="1" t="n"/>
+      <c r="AX14" s="1" t="n"/>
+      <c r="AY14" s="1" t="n"/>
+      <c r="AZ14" s="1" t="n"/>
+      <c r="BA14" s="1" t="n"/>
+      <c r="BB14" s="1" t="n"/>
+      <c r="BC14" s="1" t="n"/>
+      <c r="BD14" s="2" t="n"/>
+      <c r="BE14" s="2" t="n"/>
+      <c r="BF14" s="2" t="n"/>
+      <c r="BG14" s="2" t="n"/>
+      <c r="BH14" s="2" t="n"/>
+      <c r="BI14" s="2" t="n"/>
+      <c r="BJ14" s="2" t="n"/>
+      <c r="BK14" s="2" t="n"/>
+      <c r="BL14" s="2" t="n"/>
+      <c r="BM14" s="2" t="n"/>
+      <c r="BN14" s="3" t="n"/>
+      <c r="BO14" s="3" t="n"/>
+      <c r="BP14" s="3" t="n"/>
+      <c r="BQ14" s="3" t="n"/>
+      <c r="BR14" s="3" t="n"/>
+      <c r="BS14" s="3" t="n"/>
+      <c r="BT14" s="3" t="n"/>
+      <c r="BU14" s="3" t="n"/>
+      <c r="BV14" s="3" t="n"/>
+      <c r="BW14" s="3" t="n"/>
+      <c r="BX14" s="4" t="n"/>
+      <c r="BY14" s="4" t="n"/>
+      <c r="BZ14" s="4" t="n"/>
+      <c r="CA14" s="4" t="n"/>
+      <c r="CB14" s="4" t="n"/>
+      <c r="CC14" s="4" t="n"/>
+      <c r="CD14" s="4" t="n"/>
+      <c r="CE14" s="4" t="n"/>
+      <c r="CF14" s="4" t="n"/>
+      <c r="CG14" s="4" t="n"/>
+      <c r="CH14" s="5" t="n"/>
+      <c r="CI14" s="5" t="n"/>
+      <c r="CJ14" s="5" t="n"/>
+      <c r="CK14" s="5" t="n"/>
+      <c r="CL14" s="5" t="n"/>
+      <c r="CM14" s="5" t="n"/>
+      <c r="CN14" s="5" t="n"/>
+      <c r="CO14" s="5" t="n"/>
+      <c r="CP14" s="5" t="n"/>
+      <c r="CQ14" s="5" t="n"/>
+      <c r="CR14" s="5" t="n"/>
+      <c r="CS14" s="5" t="n"/>
+      <c r="CT14" s="5" t="n"/>
+      <c r="CU14" s="5" t="n"/>
+      <c r="CV14" s="5" t="n"/>
+      <c r="CW14" s="5" t="n"/>
+      <c r="CX14" s="5" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Maszyna 8</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="6" t="n"/>
-      <c r="R9" s="6" t="n"/>
-      <c r="S9" s="7" t="n"/>
-      <c r="T9" s="7" t="n"/>
-      <c r="U9" s="7" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7" t="n"/>
-      <c r="Z9" s="7" t="n"/>
-      <c r="AA9" s="7" t="n"/>
-      <c r="AB9" s="7" t="n"/>
-      <c r="AC9" s="8" t="n"/>
-      <c r="AD9" s="8" t="n"/>
-      <c r="AE9" s="8" t="n"/>
-      <c r="AF9" s="8" t="n"/>
-      <c r="AG9" s="8" t="n"/>
-      <c r="AH9" s="8" t="n"/>
-      <c r="AI9" s="8" t="n"/>
-      <c r="AJ9" s="8" t="n"/>
-      <c r="AK9" s="8" t="n"/>
-      <c r="AL9" s="8" t="n"/>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="9" t="n"/>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="9" t="n"/>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="9" t="n"/>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="1" t="n"/>
-      <c r="AX9" s="1" t="n"/>
-      <c r="AY9" s="1" t="n"/>
-      <c r="AZ9" s="1" t="n"/>
-      <c r="BA9" s="1" t="n"/>
-      <c r="BB9" s="1" t="n"/>
-      <c r="BC9" s="1" t="n"/>
-      <c r="BD9" s="1" t="n"/>
-      <c r="BE9" s="1" t="n"/>
-      <c r="BF9" s="1" t="n"/>
-      <c r="BG9" s="2" t="n"/>
-      <c r="BH9" s="2" t="n"/>
-      <c r="BI9" s="2" t="n"/>
-      <c r="BJ9" s="2" t="n"/>
-      <c r="BK9" s="2" t="n"/>
-      <c r="BL9" s="2" t="n"/>
-      <c r="BM9" s="2" t="n"/>
-      <c r="BN9" s="2" t="n"/>
-      <c r="BO9" s="2" t="n"/>
-      <c r="BP9" s="2" t="n"/>
-      <c r="BQ9" s="3" t="n"/>
-      <c r="BR9" s="3" t="n"/>
-      <c r="BS9" s="3" t="n"/>
-      <c r="BT9" s="3" t="n"/>
-      <c r="BU9" s="3" t="n"/>
-      <c r="BV9" s="3" t="n"/>
-      <c r="BW9" s="3" t="n"/>
-      <c r="BX9" s="3" t="n"/>
-      <c r="BY9" s="3" t="n"/>
-      <c r="BZ9" s="3" t="n"/>
-      <c r="CA9" s="4" t="n"/>
-      <c r="CB9" s="4" t="n"/>
-      <c r="CC9" s="4" t="n"/>
-      <c r="CD9" s="4" t="n"/>
-      <c r="CE9" s="4" t="n"/>
-      <c r="CF9" s="4" t="n"/>
-      <c r="CG9" s="4" t="n"/>
-      <c r="CH9" s="4" t="n"/>
-      <c r="CI9" s="4" t="n"/>
-      <c r="CJ9" s="4" t="n"/>
-      <c r="CK9" s="5" t="n"/>
-      <c r="CL9" s="5" t="n"/>
-      <c r="CM9" s="5" t="n"/>
-      <c r="CN9" s="5" t="n"/>
-      <c r="CO9" s="5" t="n"/>
-      <c r="CP9" s="5" t="n"/>
-      <c r="CQ9" s="5" t="n"/>
-      <c r="CR9" s="5" t="n"/>
-      <c r="CS9" s="5" t="n"/>
-      <c r="CT9" s="5" t="n"/>
-      <c r="CU9" s="5" t="n"/>
-      <c r="CV9" s="5" t="n"/>
-      <c r="CW9" s="5" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="7" t="n"/>
+      <c r="T16" s="7" t="n"/>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="7" t="n"/>
+      <c r="W16" s="7" t="n"/>
+      <c r="X16" s="7" t="n"/>
+      <c r="Y16" s="7" t="n"/>
+      <c r="Z16" s="7" t="n"/>
+      <c r="AA16" s="7" t="n"/>
+      <c r="AB16" s="7" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8" t="n"/>
+      <c r="AI16" s="8" t="n"/>
+      <c r="AJ16" s="8" t="n"/>
+      <c r="AK16" s="8" t="n"/>
+      <c r="AL16" s="8" t="n"/>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="9" t="n"/>
+      <c r="AP16" s="9" t="n"/>
+      <c r="AQ16" s="9" t="n"/>
+      <c r="AR16" s="9" t="n"/>
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="9" t="n"/>
+      <c r="AU16" s="9" t="n"/>
+      <c r="AV16" s="9" t="n"/>
+      <c r="AW16" s="1" t="n"/>
+      <c r="AX16" s="1" t="n"/>
+      <c r="AY16" s="1" t="n"/>
+      <c r="AZ16" s="1" t="n"/>
+      <c r="BA16" s="1" t="n"/>
+      <c r="BB16" s="1" t="n"/>
+      <c r="BC16" s="1" t="n"/>
+      <c r="BD16" s="1" t="n"/>
+      <c r="BE16" s="1" t="n"/>
+      <c r="BF16" s="1" t="n"/>
+      <c r="BG16" s="2" t="n"/>
+      <c r="BH16" s="2" t="n"/>
+      <c r="BI16" s="2" t="n"/>
+      <c r="BJ16" s="2" t="n"/>
+      <c r="BK16" s="2" t="n"/>
+      <c r="BL16" s="2" t="n"/>
+      <c r="BM16" s="2" t="n"/>
+      <c r="BN16" s="2" t="n"/>
+      <c r="BO16" s="2" t="n"/>
+      <c r="BP16" s="2" t="n"/>
+      <c r="BQ16" s="3" t="n"/>
+      <c r="BR16" s="3" t="n"/>
+      <c r="BS16" s="3" t="n"/>
+      <c r="BT16" s="3" t="n"/>
+      <c r="BU16" s="3" t="n"/>
+      <c r="BV16" s="3" t="n"/>
+      <c r="BW16" s="3" t="n"/>
+      <c r="BX16" s="3" t="n"/>
+      <c r="BY16" s="3" t="n"/>
+      <c r="BZ16" s="3" t="n"/>
+      <c r="CA16" s="4" t="n"/>
+      <c r="CB16" s="4" t="n"/>
+      <c r="CC16" s="4" t="n"/>
+      <c r="CD16" s="4" t="n"/>
+      <c r="CE16" s="4" t="n"/>
+      <c r="CF16" s="4" t="n"/>
+      <c r="CG16" s="4" t="n"/>
+      <c r="CH16" s="4" t="n"/>
+      <c r="CI16" s="4" t="n"/>
+      <c r="CJ16" s="4" t="n"/>
+      <c r="CK16" s="5" t="n"/>
+      <c r="CL16" s="5" t="n"/>
+      <c r="CM16" s="5" t="n"/>
+      <c r="CN16" s="5" t="n"/>
+      <c r="CO16" s="5" t="n"/>
+      <c r="CP16" s="5" t="n"/>
+      <c r="CQ16" s="5" t="n"/>
+      <c r="CR16" s="5" t="n"/>
+      <c r="CS16" s="5" t="n"/>
+      <c r="CT16" s="5" t="n"/>
+      <c r="CU16" s="5" t="n"/>
+      <c r="CV16" s="5" t="n"/>
+      <c r="CW16" s="5" t="n"/>
+      <c r="CX16" s="5" t="n"/>
     </row>
-    <row r="10">
-      <c r="B10" s="10" t="n">
+    <row r="17">
+      <c r="B17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D17" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F17" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H17" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I17" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J17" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K17" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M17" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N17" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="O17" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="P10" s="10" t="n">
+      <c r="P17" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q17" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="R17" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="S10" s="10" t="n">
+      <c r="S17" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="T10" s="10" t="n">
+      <c r="T17" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="U10" s="10" t="n">
+      <c r="U17" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V17" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W17" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="X10" s="10" t="n">
+      <c r="X17" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="Y10" s="10" t="n">
+      <c r="Y17" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="Z10" s="10" t="n">
+      <c r="Z17" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="AA10" s="10" t="n">
+      <c r="AA17" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="AB10" s="10" t="n">
+      <c r="AB17" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="AC10" s="10" t="n">
+      <c r="AC17" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="AD10" s="10" t="n">
+      <c r="AD17" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="AE10" s="10" t="n">
+      <c r="AE17" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="AF10" s="10" t="n">
+      <c r="AF17" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="AG10" s="10" t="n">
+      <c r="AG17" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="AH10" s="10" t="n">
+      <c r="AH17" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="AI10" s="10" t="n">
+      <c r="AI17" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="AJ10" s="10" t="n">
+      <c r="AJ17" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="AK10" s="10" t="n">
+      <c r="AK17" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="AL10" s="10" t="n">
+      <c r="AL17" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="AM10" s="10" t="n">
+      <c r="AM17" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="AN10" s="10" t="n">
+      <c r="AN17" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="AO10" s="10" t="n">
+      <c r="AO17" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="AP10" s="10" t="n">
+      <c r="AP17" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="AQ10" s="10" t="n">
+      <c r="AQ17" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="AR10" s="10" t="n">
+      <c r="AR17" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="AS10" s="10" t="n">
+      <c r="AS17" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="AT10" s="10" t="n">
+      <c r="AT17" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="AU10" s="10" t="n">
+      <c r="AU17" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="AV10" s="10" t="n">
+      <c r="AV17" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="AW10" s="10" t="n">
+      <c r="AW17" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="AX10" s="10" t="n">
+      <c r="AX17" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="AY10" s="10" t="n">
+      <c r="AY17" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="AZ10" s="10" t="n">
+      <c r="AZ17" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="BA10" s="10" t="n">
+      <c r="BA17" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="BB10" s="10" t="n">
+      <c r="BB17" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="BC10" s="10" t="n">
+      <c r="BC17" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="BD10" s="10" t="n">
+      <c r="BD17" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="BE10" s="10" t="n">
+      <c r="BE17" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="BF10" s="10" t="n">
+      <c r="BF17" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="BG10" s="10" t="n">
+      <c r="BG17" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="BH10" s="10" t="n">
+      <c r="BH17" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="BI10" s="10" t="n">
+      <c r="BI17" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="BJ10" s="10" t="n">
+      <c r="BJ17" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="BK10" s="10" t="n">
+      <c r="BK17" s="10" t="n">
         <v>61</v>
       </c>
-      <c r="BL10" s="10" t="n">
+      <c r="BL17" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="BM10" s="10" t="n">
+      <c r="BM17" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="BN10" s="10" t="n">
+      <c r="BN17" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="BO10" s="10" t="n">
+      <c r="BO17" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="BP10" s="10" t="n">
+      <c r="BP17" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="BQ10" s="10" t="n">
+      <c r="BQ17" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="BR10" s="10" t="n">
+      <c r="BR17" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="BS10" s="10" t="n">
+      <c r="BS17" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="BT10" s="10" t="n">
+      <c r="BT17" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="BU10" s="10" t="n">
+      <c r="BU17" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="BV10" s="10" t="n">
+      <c r="BV17" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="BW10" s="10" t="n">
+      <c r="BW17" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="BX10" s="10" t="n">
+      <c r="BX17" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="BY10" s="10" t="n">
+      <c r="BY17" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="BZ10" s="10" t="n">
+      <c r="BZ17" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="CA10" s="10" t="n">
+      <c r="CA17" s="10" t="n">
         <v>77</v>
       </c>
-      <c r="CB10" s="10" t="n">
+      <c r="CB17" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="CC10" s="10" t="n">
+      <c r="CC17" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="CD10" s="10" t="n">
+      <c r="CD17" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="CE10" s="10" t="n">
+      <c r="CE17" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="CF10" s="10" t="n">
+      <c r="CF17" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="CG10" s="10" t="n">
+      <c r="CG17" s="10" t="n">
         <v>83</v>
       </c>
-      <c r="CH10" s="10" t="n">
+      <c r="CH17" s="10" t="n">
         <v>84</v>
       </c>
-      <c r="CI10" s="10" t="n">
+      <c r="CI17" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="CJ10" s="10" t="n">
+      <c r="CJ17" s="10" t="n">
         <v>86</v>
       </c>
-      <c r="CK10" s="10" t="n">
+      <c r="CK17" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="CL10" s="10" t="n">
+      <c r="CL17" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="CM10" s="10" t="n">
+      <c r="CM17" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="CN10" s="10" t="n">
+      <c r="CN17" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="CO10" s="10" t="n">
+      <c r="CO17" s="10" t="n">
         <v>91</v>
       </c>
-      <c r="CP10" s="10" t="n">
+      <c r="CP17" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="CQ10" s="10" t="n">
+      <c r="CQ17" s="10" t="n">
         <v>93</v>
       </c>
-      <c r="CR10" s="10" t="n">
+      <c r="CR17" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="CS10" s="10" t="n">
+      <c r="CS17" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="CT10" s="10" t="n">
+      <c r="CT17" s="10" t="n">
         <v>96</v>
       </c>
-      <c r="CU10" s="10" t="n">
+      <c r="CU17" s="10" t="n">
         <v>97</v>
       </c>
-      <c r="CV10" s="10" t="n">
+      <c r="CV17" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="CW10" s="10" t="n">
+      <c r="CW17" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="CX10" s="10" t="n">
+      <c r="CX17" s="10" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Zadania:</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Zadanie 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Zadanie 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Zadanie 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Zadanie 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Zadanie 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Zadanie 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Zadanie 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Zadanie 8</t>
         </is>
       </c>
     </row>
@@ -1821,6 +1774,62 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Zadanie 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Zadanie 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Zadanie 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Zadanie 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Zadanie 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Zadanie 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Zadanie 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Zadanie 9</t>
         </is>
       </c>
